--- a/backend/data/oficinas_ba.xlsx
+++ b/backend/data/oficinas_ba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSA Área TI\Documents\CSA\Epicollect\Generacion_informes\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9766486E-3034-49AD-B98E-D9DEE66BE4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA5DECE-5526-492B-A413-64EE9B24DCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B056019-2FF6-4E05-9E45-B7C25F0E6A03}"/>
   </bookViews>
@@ -9734,7 +9734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9786,6 +9786,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10004,7 +10012,7 @@
   <dimension ref="A1:M1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="23" customWidth="1"/>
     <col min="2" max="2" width="47.140625" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="5" width="10.5703125" customWidth="1"/>
@@ -10016,7 +10024,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -10057,7 +10065,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="9">
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -10098,7 +10106,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="9">
         <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -10139,7 +10147,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="9">
         <v>70</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -10180,7 +10188,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="9">
         <v>230</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -10221,7 +10229,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="9">
         <v>250</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -10262,7 +10270,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="9">
         <v>260</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -10303,7 +10311,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="9">
         <v>280</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -10344,7 +10352,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="9">
         <v>290</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -10385,7 +10393,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="9">
         <v>360</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -10426,7 +10434,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="9">
         <v>590</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -10467,7 +10475,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="9">
         <v>700</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -10508,7 +10516,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="9">
         <v>730</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -10549,7 +10557,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="9">
         <v>750</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -10590,7 +10598,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="A15" s="9">
         <v>820</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -10631,7 +10639,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="9">
         <v>850</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -10672,7 +10680,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="A17" s="9">
         <v>890</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -10713,7 +10721,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="9">
         <v>900</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -10754,7 +10762,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="A19" s="9">
         <v>910</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -10795,7 +10803,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="9">
         <v>920</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -10836,7 +10844,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="9">
         <v>940</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -10877,7 +10885,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="9">
         <v>960</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -10918,7 +10926,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="A23" s="9">
         <v>970</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -10959,7 +10967,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="9">
         <v>980</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -11000,7 +11008,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="A25" s="9">
         <v>1203</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -11041,7 +11049,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="9">
         <v>1204</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -11082,7 +11090,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="A27" s="9">
         <v>1205</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -11123,7 +11131,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="9">
         <v>1207</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -11164,7 +11172,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+      <c r="A29" s="9">
         <v>1215</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -11205,7 +11213,7 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="A30" s="9">
         <v>1216</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -11246,7 +11254,7 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="22">
         <v>1218</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -11287,7 +11295,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="A32" s="9">
         <v>1230</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -11328,7 +11336,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="A33" s="9">
         <v>1240</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -11369,7 +11377,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="A34" s="9">
         <v>1243</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -11410,7 +11418,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+      <c r="A35" s="9">
         <v>1244</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -11451,7 +11459,7 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="A36" s="9">
         <v>1246</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -11492,7 +11500,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="A37" s="9">
         <v>1250</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -11533,7 +11541,7 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="A38" s="9">
         <v>1255</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -11574,7 +11582,7 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+      <c r="A39" s="9">
         <v>1260</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -11615,7 +11623,7 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+      <c r="A40" s="9">
         <v>1263</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -11656,7 +11664,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+      <c r="A41" s="9">
         <v>1265</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -11697,7 +11705,7 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+      <c r="A42" s="9">
         <v>1267</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -11738,7 +11746,7 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+      <c r="A43" s="9">
         <v>1270</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -11779,7 +11787,7 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+      <c r="A44" s="9">
         <v>1301</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -11820,7 +11828,7 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+      <c r="A45" s="9">
         <v>1302</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -11861,7 +11869,7 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+      <c r="A46" s="9">
         <v>1303</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -11902,7 +11910,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+      <c r="A47" s="9">
         <v>1305</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -11943,7 +11951,7 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="A48" s="9">
         <v>1307</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -11984,7 +11992,7 @@
       </c>
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+      <c r="A49" s="9">
         <v>1309</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -12025,7 +12033,7 @@
       </c>
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+      <c r="A50" s="9">
         <v>1314</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -12066,7 +12074,7 @@
       </c>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+      <c r="A51" s="9">
         <v>1316</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -12107,7 +12115,7 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+      <c r="A52" s="9">
         <v>1317</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -12148,7 +12156,7 @@
       </c>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="22">
         <v>1318</v>
       </c>
       <c r="B53" s="7" t="s">
@@ -12189,7 +12197,7 @@
       </c>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+      <c r="A54" s="9">
         <v>1320</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -12230,7 +12238,7 @@
       </c>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+      <c r="A55" s="9">
         <v>1321</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -12271,7 +12279,7 @@
       </c>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+      <c r="A56" s="9">
         <v>1323</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -12312,7 +12320,7 @@
       </c>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+      <c r="A57" s="9">
         <v>1324</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -12353,7 +12361,7 @@
       </c>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+      <c r="A58" s="9">
         <v>1325</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -12394,7 +12402,7 @@
       </c>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+      <c r="A59" s="9">
         <v>1326</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -12435,7 +12443,7 @@
       </c>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+      <c r="A60" s="9">
         <v>1330</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -12476,7 +12484,7 @@
       </c>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+      <c r="A61" s="9">
         <v>1331</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -12517,7 +12525,7 @@
       </c>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+      <c r="A62" s="9">
         <v>1332</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -12558,7 +12566,7 @@
       </c>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="22">
         <v>1334</v>
       </c>
       <c r="B63" s="7" t="s">
@@ -12599,7 +12607,7 @@
       </c>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+      <c r="A64" s="9">
         <v>1336</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -12640,7 +12648,7 @@
       </c>
     </row>
     <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+      <c r="A65" s="9">
         <v>1340</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -12681,7 +12689,7 @@
       </c>
     </row>
     <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+      <c r="A66" s="9">
         <v>1341</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -12722,7 +12730,7 @@
       </c>
     </row>
     <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+      <c r="A67" s="9">
         <v>1342</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -12763,7 +12771,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+      <c r="A68" s="9">
         <v>1345</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -12804,7 +12812,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+      <c r="A69" s="9">
         <v>1346</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -12845,7 +12853,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+      <c r="A70" s="9">
         <v>1348</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -12886,7 +12894,7 @@
       </c>
     </row>
     <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+      <c r="A71" s="9">
         <v>1349</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -12927,7 +12935,7 @@
       </c>
     </row>
     <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+      <c r="A72" s="9">
         <v>1350</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -12968,7 +12976,7 @@
       </c>
     </row>
     <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+      <c r="A73" s="9">
         <v>1351</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -13009,7 +13017,7 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+      <c r="A74" s="9">
         <v>1352</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -13050,7 +13058,7 @@
       </c>
     </row>
     <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+      <c r="A75" s="9">
         <v>1353</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -13091,7 +13099,7 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+      <c r="A76" s="9">
         <v>1354</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -13132,7 +13140,7 @@
       </c>
     </row>
     <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+      <c r="A77" s="9">
         <v>1355</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -13173,7 +13181,7 @@
       </c>
     </row>
     <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+      <c r="A78" s="9">
         <v>1356</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -13214,7 +13222,7 @@
       </c>
     </row>
     <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
+      <c r="A79" s="9">
         <v>1357</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -13255,7 +13263,7 @@
       </c>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
+      <c r="A80" s="9">
         <v>1359</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -13296,7 +13304,7 @@
       </c>
     </row>
     <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+      <c r="A81" s="9">
         <v>1360</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -13337,7 +13345,7 @@
       </c>
     </row>
     <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+      <c r="A82" s="9">
         <v>1361</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -13378,7 +13386,7 @@
       </c>
     </row>
     <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
+      <c r="A83" s="9">
         <v>1362</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -13419,7 +13427,7 @@
       </c>
     </row>
     <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+      <c r="A84" s="9">
         <v>1363</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -13460,7 +13468,7 @@
       </c>
     </row>
     <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+      <c r="A85" s="9">
         <v>1365</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -13501,7 +13509,7 @@
       </c>
     </row>
     <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+      <c r="A86" s="9">
         <v>1366</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -13542,7 +13550,7 @@
       </c>
     </row>
     <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
+      <c r="A87" s="9">
         <v>1368</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -13583,7 +13591,7 @@
       </c>
     </row>
     <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
+      <c r="A88" s="9">
         <v>1370</v>
       </c>
       <c r="B88" s="4" t="s">
@@ -13624,7 +13632,7 @@
       </c>
     </row>
     <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
+      <c r="A89" s="9">
         <v>1371</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -13665,7 +13673,7 @@
       </c>
     </row>
     <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
+      <c r="A90" s="9">
         <v>1372</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -13706,7 +13714,7 @@
       </c>
     </row>
     <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
+      <c r="A91" s="9">
         <v>1374</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -13747,7 +13755,7 @@
       </c>
     </row>
     <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+      <c r="A92" s="9">
         <v>1375</v>
       </c>
       <c r="B92" s="4" t="s">
@@ -13788,7 +13796,7 @@
       </c>
     </row>
     <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+      <c r="A93" s="9">
         <v>1377</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -13829,7 +13837,7 @@
       </c>
     </row>
     <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+      <c r="A94" s="9">
         <v>1378</v>
       </c>
       <c r="B94" s="4" t="s">
@@ -13870,7 +13878,7 @@
       </c>
     </row>
     <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+      <c r="A95" s="9">
         <v>1379</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -13911,7 +13919,7 @@
       </c>
     </row>
     <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
+      <c r="A96" s="9">
         <v>1380</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -13952,7 +13960,7 @@
       </c>
     </row>
     <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
+      <c r="A97" s="9">
         <v>1381</v>
       </c>
       <c r="B97" s="4" t="s">
@@ -13993,7 +14001,7 @@
       </c>
     </row>
     <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
+      <c r="A98" s="9">
         <v>1382</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -14034,7 +14042,7 @@
       </c>
     </row>
     <row r="99" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+      <c r="A99" s="9">
         <v>1383</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -14075,7 +14083,7 @@
       </c>
     </row>
     <row r="100" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
+      <c r="A100" s="9">
         <v>1385</v>
       </c>
       <c r="B100" s="4" t="s">
@@ -14116,7 +14124,7 @@
       </c>
     </row>
     <row r="101" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+      <c r="A101" s="9">
         <v>1386</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -14157,7 +14165,7 @@
       </c>
     </row>
     <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
+      <c r="A102" s="9">
         <v>1387</v>
       </c>
       <c r="B102" s="4" t="s">
@@ -14198,7 +14206,7 @@
       </c>
     </row>
     <row r="103" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
+      <c r="A103" s="9">
         <v>1388</v>
       </c>
       <c r="B103" s="4" t="s">
@@ -14239,7 +14247,7 @@
       </c>
     </row>
     <row r="104" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
+      <c r="A104" s="9">
         <v>1389</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -14280,7 +14288,7 @@
       </c>
     </row>
     <row r="105" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
+      <c r="A105" s="9">
         <v>1390</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -14321,7 +14329,7 @@
       </c>
     </row>
     <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
+      <c r="A106" s="9">
         <v>1391</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -14362,7 +14370,7 @@
       </c>
     </row>
     <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
+      <c r="A107" s="9">
         <v>1392</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -14403,7 +14411,7 @@
       </c>
     </row>
     <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+      <c r="A108" s="9">
         <v>1393</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -14444,7 +14452,7 @@
       </c>
     </row>
     <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+      <c r="A109" s="9">
         <v>1394</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -14485,7 +14493,7 @@
       </c>
     </row>
     <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+      <c r="A110" s="9">
         <v>1395</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -14526,7 +14534,7 @@
       </c>
     </row>
     <row r="111" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+      <c r="A111" s="9">
         <v>1396</v>
       </c>
       <c r="B111" s="4" t="s">
@@ -14567,7 +14575,7 @@
       </c>
     </row>
     <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
+      <c r="A112" s="9">
         <v>1397</v>
       </c>
       <c r="B112" s="4" t="s">
@@ -14608,7 +14616,7 @@
       </c>
     </row>
     <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
+      <c r="A113" s="9">
         <v>1398</v>
       </c>
       <c r="B113" s="4" t="s">
@@ -14649,7 +14657,7 @@
       </c>
     </row>
     <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+      <c r="A114" s="9">
         <v>1399</v>
       </c>
       <c r="B114" s="4" t="s">
@@ -14690,7 +14698,7 @@
       </c>
     </row>
     <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
+      <c r="A115" s="9">
         <v>1401</v>
       </c>
       <c r="B115" s="4" t="s">
@@ -14731,7 +14739,7 @@
       </c>
     </row>
     <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
+      <c r="A116" s="9">
         <v>1410</v>
       </c>
       <c r="B116" s="4" t="s">
@@ -14772,7 +14780,7 @@
       </c>
     </row>
     <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+      <c r="A117" s="9">
         <v>1412</v>
       </c>
       <c r="B117" s="4" t="s">
@@ -14813,7 +14821,7 @@
       </c>
     </row>
     <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+      <c r="A118" s="9">
         <v>1414</v>
       </c>
       <c r="B118" s="4" t="s">
@@ -14854,7 +14862,7 @@
       </c>
     </row>
     <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+      <c r="A119" s="9">
         <v>1415</v>
       </c>
       <c r="B119" s="4" t="s">
@@ -14895,7 +14903,7 @@
       </c>
     </row>
     <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
+      <c r="A120" s="9">
         <v>1420</v>
       </c>
       <c r="B120" s="4" t="s">
@@ -14936,7 +14944,7 @@
       </c>
     </row>
     <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
+      <c r="A121" s="9">
         <v>1422</v>
       </c>
       <c r="B121" s="4" t="s">
@@ -14977,7 +14985,7 @@
       </c>
     </row>
     <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
+      <c r="A122" s="9">
         <v>1424</v>
       </c>
       <c r="B122" s="4" t="s">
@@ -15018,7 +15026,7 @@
       </c>
     </row>
     <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
+      <c r="A123" s="9">
         <v>1426</v>
       </c>
       <c r="B123" s="4" t="s">
@@ -15059,7 +15067,7 @@
       </c>
     </row>
     <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="22">
         <v>1428</v>
       </c>
       <c r="B124" s="7" t="s">
@@ -15100,7 +15108,7 @@
       </c>
     </row>
     <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="22">
         <v>1430</v>
       </c>
       <c r="B125" s="7" t="s">
@@ -15141,7 +15149,7 @@
       </c>
     </row>
     <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
+      <c r="A126" s="9">
         <v>1435</v>
       </c>
       <c r="B126" s="4" t="s">
@@ -15182,7 +15190,7 @@
       </c>
     </row>
     <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
+      <c r="A127" s="9">
         <v>1438</v>
       </c>
       <c r="B127" s="4" t="s">
@@ -15223,7 +15231,7 @@
       </c>
     </row>
     <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="3">
+      <c r="A128" s="9">
         <v>1442</v>
       </c>
       <c r="B128" s="4" t="s">
@@ -15264,7 +15272,7 @@
       </c>
     </row>
     <row r="129" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="22">
         <v>1444</v>
       </c>
       <c r="B129" s="7" t="s">
@@ -15305,7 +15313,7 @@
       </c>
     </row>
     <row r="130" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="3">
+      <c r="A130" s="9">
         <v>1446</v>
       </c>
       <c r="B130" s="4" t="s">
@@ -15346,7 +15354,7 @@
       </c>
     </row>
     <row r="131" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
+      <c r="A131" s="9">
         <v>1448</v>
       </c>
       <c r="B131" s="4" t="s">
@@ -15387,7 +15395,7 @@
       </c>
     </row>
     <row r="132" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+      <c r="A132" s="9">
         <v>1450</v>
       </c>
       <c r="B132" s="4" t="s">
@@ -15428,7 +15436,7 @@
       </c>
     </row>
     <row r="133" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="3">
+      <c r="A133" s="9">
         <v>1452</v>
       </c>
       <c r="B133" s="4" t="s">
@@ -15469,7 +15477,7 @@
       </c>
     </row>
     <row r="134" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="3">
+      <c r="A134" s="9">
         <v>1454</v>
       </c>
       <c r="B134" s="4" t="s">
@@ -15510,7 +15518,7 @@
       </c>
     </row>
     <row r="135" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="3">
+      <c r="A135" s="9">
         <v>1456</v>
       </c>
       <c r="B135" s="4" t="s">
@@ -15551,7 +15559,7 @@
       </c>
     </row>
     <row r="136" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="3">
+      <c r="A136" s="9">
         <v>1460</v>
       </c>
       <c r="B136" s="4" t="s">
@@ -15592,7 +15600,7 @@
       </c>
     </row>
     <row r="137" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="3">
+      <c r="A137" s="9">
         <v>1462</v>
       </c>
       <c r="B137" s="4" t="s">
@@ -15633,7 +15641,7 @@
       </c>
     </row>
     <row r="138" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="3">
+      <c r="A138" s="9">
         <v>1466</v>
       </c>
       <c r="B138" s="4" t="s">
@@ -15674,7 +15682,7 @@
       </c>
     </row>
     <row r="139" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="3">
+      <c r="A139" s="9">
         <v>1470</v>
       </c>
       <c r="B139" s="4" t="s">
@@ -15715,7 +15723,7 @@
       </c>
     </row>
     <row r="140" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="3">
+      <c r="A140" s="9">
         <v>1471</v>
       </c>
       <c r="B140" s="4" t="s">
@@ -15756,7 +15764,7 @@
       </c>
     </row>
     <row r="141" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="22">
         <v>1472</v>
       </c>
       <c r="B141" s="7" t="s">
@@ -15797,7 +15805,7 @@
       </c>
     </row>
     <row r="142" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="3">
+      <c r="A142" s="9">
         <v>1474</v>
       </c>
       <c r="B142" s="4" t="s">
@@ -15838,7 +15846,7 @@
       </c>
     </row>
     <row r="143" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="3">
+      <c r="A143" s="9">
         <v>1476</v>
       </c>
       <c r="B143" s="4" t="s">
@@ -15879,7 +15887,7 @@
       </c>
     </row>
     <row r="144" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="3">
+      <c r="A144" s="9">
         <v>1478</v>
       </c>
       <c r="B144" s="4" t="s">
@@ -15920,7 +15928,7 @@
       </c>
     </row>
     <row r="145" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="3">
+      <c r="A145" s="9">
         <v>1480</v>
       </c>
       <c r="B145" s="4" t="s">
@@ -15961,7 +15969,7 @@
       </c>
     </row>
     <row r="146" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="3">
+      <c r="A146" s="9">
         <v>1482</v>
       </c>
       <c r="B146" s="4" t="s">
@@ -16002,7 +16010,7 @@
       </c>
     </row>
     <row r="147" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="3">
+      <c r="A147" s="9">
         <v>1484</v>
       </c>
       <c r="B147" s="4" t="s">
@@ -16043,7 +16051,7 @@
       </c>
     </row>
     <row r="148" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="3">
+      <c r="A148" s="9">
         <v>1486</v>
       </c>
       <c r="B148" s="4" t="s">
@@ -16084,7 +16092,7 @@
       </c>
     </row>
     <row r="149" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="3">
+      <c r="A149" s="9">
         <v>1487</v>
       </c>
       <c r="B149" s="4" t="s">
@@ -16125,7 +16133,7 @@
       </c>
     </row>
     <row r="150" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="3">
+      <c r="A150" s="9">
         <v>1501</v>
       </c>
       <c r="B150" s="4" t="s">
@@ -16166,7 +16174,7 @@
       </c>
     </row>
     <row r="151" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="3">
+      <c r="A151" s="9">
         <v>1502</v>
       </c>
       <c r="B151" s="4" t="s">
@@ -16207,7 +16215,7 @@
       </c>
     </row>
     <row r="152" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="3">
+      <c r="A152" s="9">
         <v>1503</v>
       </c>
       <c r="B152" s="4" t="s">
@@ -16248,7 +16256,7 @@
       </c>
     </row>
     <row r="153" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="3">
+      <c r="A153" s="9">
         <v>1504</v>
       </c>
       <c r="B153" s="4" t="s">
@@ -16289,7 +16297,7 @@
       </c>
     </row>
     <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="3">
+      <c r="A154" s="9">
         <v>1505</v>
       </c>
       <c r="B154" s="4" t="s">
@@ -16330,7 +16338,7 @@
       </c>
     </row>
     <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="3">
+      <c r="A155" s="9">
         <v>1506</v>
       </c>
       <c r="B155" s="4" t="s">
@@ -16371,7 +16379,7 @@
       </c>
     </row>
     <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="3">
+      <c r="A156" s="9">
         <v>1507</v>
       </c>
       <c r="B156" s="4" t="s">
@@ -16412,7 +16420,7 @@
       </c>
     </row>
     <row r="157" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="3">
+      <c r="A157" s="9">
         <v>1509</v>
       </c>
       <c r="B157" s="4" t="s">
@@ -16453,7 +16461,7 @@
       </c>
     </row>
     <row r="158" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
+      <c r="A158" s="9">
         <v>1510</v>
       </c>
       <c r="B158" s="4" t="s">
@@ -16494,7 +16502,7 @@
       </c>
     </row>
     <row r="159" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="3">
+      <c r="A159" s="9">
         <v>1511</v>
       </c>
       <c r="B159" s="4" t="s">
@@ -16535,7 +16543,7 @@
       </c>
     </row>
     <row r="160" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="3">
+      <c r="A160" s="9">
         <v>1512</v>
       </c>
       <c r="B160" s="4" t="s">
@@ -16576,7 +16584,7 @@
       </c>
     </row>
     <row r="161" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="3">
+      <c r="A161" s="9">
         <v>1514</v>
       </c>
       <c r="B161" s="4" t="s">
@@ -16617,7 +16625,7 @@
       </c>
     </row>
     <row r="162" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="3">
+      <c r="A162" s="9">
         <v>1515</v>
       </c>
       <c r="B162" s="4" t="s">
@@ -16658,7 +16666,7 @@
       </c>
     </row>
     <row r="163" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="3">
+      <c r="A163" s="9">
         <v>1516</v>
       </c>
       <c r="B163" s="4" t="s">
@@ -16699,7 +16707,7 @@
       </c>
     </row>
     <row r="164" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="3">
+      <c r="A164" s="9">
         <v>1518</v>
       </c>
       <c r="B164" s="4" t="s">
@@ -16740,7 +16748,7 @@
       </c>
     </row>
     <row r="165" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="3">
+      <c r="A165" s="9">
         <v>1520</v>
       </c>
       <c r="B165" s="4" t="s">
@@ -16781,7 +16789,7 @@
       </c>
     </row>
     <row r="166" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="3">
+      <c r="A166" s="9">
         <v>1522</v>
       </c>
       <c r="B166" s="4" t="s">
@@ -16822,7 +16830,7 @@
       </c>
     </row>
     <row r="167" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="3">
+      <c r="A167" s="9">
         <v>1524</v>
       </c>
       <c r="B167" s="4" t="s">
@@ -16863,7 +16871,7 @@
       </c>
     </row>
     <row r="168" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="3">
+      <c r="A168" s="9">
         <v>1526</v>
       </c>
       <c r="B168" s="4" t="s">
@@ -16904,7 +16912,7 @@
       </c>
     </row>
     <row r="169" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="3">
+      <c r="A169" s="9">
         <v>1528</v>
       </c>
       <c r="B169" s="4" t="s">
@@ -16945,7 +16953,7 @@
       </c>
     </row>
     <row r="170" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="3">
+      <c r="A170" s="9">
         <v>1530</v>
       </c>
       <c r="B170" s="4" t="s">
@@ -16986,7 +16994,7 @@
       </c>
     </row>
     <row r="171" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="3">
+      <c r="A171" s="9">
         <v>1532</v>
       </c>
       <c r="B171" s="4" t="s">
@@ -17027,7 +17035,7 @@
       </c>
     </row>
     <row r="172" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="3">
+      <c r="A172" s="9">
         <v>1534</v>
       </c>
       <c r="B172" s="4" t="s">
@@ -17068,7 +17076,7 @@
       </c>
     </row>
     <row r="173" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="3">
+      <c r="A173" s="9">
         <v>1535</v>
       </c>
       <c r="B173" s="4" t="s">
@@ -17109,7 +17117,7 @@
       </c>
     </row>
     <row r="174" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="3">
+      <c r="A174" s="9">
         <v>1536</v>
       </c>
       <c r="B174" s="4" t="s">
@@ -17150,7 +17158,7 @@
       </c>
     </row>
     <row r="175" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="3">
+      <c r="A175" s="9">
         <v>1538</v>
       </c>
       <c r="B175" s="4" t="s">
@@ -17191,7 +17199,7 @@
       </c>
     </row>
     <row r="176" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="3">
+      <c r="A176" s="9">
         <v>1540</v>
       </c>
       <c r="B176" s="4" t="s">
@@ -17232,7 +17240,7 @@
       </c>
     </row>
     <row r="177" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="3">
+      <c r="A177" s="9">
         <v>1542</v>
       </c>
       <c r="B177" s="4" t="s">
@@ -17273,7 +17281,7 @@
       </c>
     </row>
     <row r="178" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="3">
+      <c r="A178" s="9">
         <v>1544</v>
       </c>
       <c r="B178" s="4" t="s">
@@ -17314,7 +17322,7 @@
       </c>
     </row>
     <row r="179" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="22">
         <v>1545</v>
       </c>
       <c r="B179" s="7" t="s">
@@ -17355,7 +17363,7 @@
       </c>
     </row>
     <row r="180" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="3">
+      <c r="A180" s="9">
         <v>1546</v>
       </c>
       <c r="B180" s="4" t="s">
@@ -17396,7 +17404,7 @@
       </c>
     </row>
     <row r="181" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="3">
+      <c r="A181" s="9">
         <v>1547</v>
       </c>
       <c r="B181" s="4" t="s">
@@ -17437,7 +17445,7 @@
       </c>
     </row>
     <row r="182" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="3">
+      <c r="A182" s="9">
         <v>1548</v>
       </c>
       <c r="B182" s="4" t="s">
@@ -17478,7 +17486,7 @@
       </c>
     </row>
     <row r="183" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="3">
+      <c r="A183" s="9">
         <v>1550</v>
       </c>
       <c r="B183" s="4" t="s">
@@ -17519,7 +17527,7 @@
       </c>
     </row>
     <row r="184" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="3">
+      <c r="A184" s="9">
         <v>1551</v>
       </c>
       <c r="B184" s="4" t="s">
@@ -17560,7 +17568,7 @@
       </c>
     </row>
     <row r="185" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="3">
+      <c r="A185" s="9">
         <v>1552</v>
       </c>
       <c r="B185" s="4" t="s">
@@ -17601,7 +17609,7 @@
       </c>
     </row>
     <row r="186" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="3">
+      <c r="A186" s="9">
         <v>1553</v>
       </c>
       <c r="B186" s="4" t="s">
@@ -17642,7 +17650,7 @@
       </c>
     </row>
     <row r="187" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="3">
+      <c r="A187" s="9">
         <v>1554</v>
       </c>
       <c r="B187" s="4" t="s">
@@ -17683,7 +17691,7 @@
       </c>
     </row>
     <row r="188" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="3">
+      <c r="A188" s="9">
         <v>1555</v>
       </c>
       <c r="B188" s="4" t="s">
@@ -17724,7 +17732,7 @@
       </c>
     </row>
     <row r="189" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="3">
+      <c r="A189" s="9">
         <v>1556</v>
       </c>
       <c r="B189" s="4" t="s">
@@ -17765,7 +17773,7 @@
       </c>
     </row>
     <row r="190" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="3">
+      <c r="A190" s="9">
         <v>1560</v>
       </c>
       <c r="B190" s="4" t="s">
@@ -17806,7 +17814,7 @@
       </c>
     </row>
     <row r="191" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="3">
+      <c r="A191" s="9">
         <v>1563</v>
       </c>
       <c r="B191" s="4" t="s">
@@ -17847,7 +17855,7 @@
       </c>
     </row>
     <row r="192" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="3">
+      <c r="A192" s="9">
         <v>1567</v>
       </c>
       <c r="B192" s="4" t="s">
@@ -17888,7 +17896,7 @@
       </c>
     </row>
     <row r="193" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="3">
+      <c r="A193" s="9">
         <v>1568</v>
       </c>
       <c r="B193" s="4" t="s">
@@ -17929,7 +17937,7 @@
       </c>
     </row>
     <row r="194" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="3">
+      <c r="A194" s="9">
         <v>1569</v>
       </c>
       <c r="B194" s="4" t="s">
@@ -17970,7 +17978,7 @@
       </c>
     </row>
     <row r="195" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="3">
+      <c r="A195" s="9">
         <v>1570</v>
       </c>
       <c r="B195" s="4" t="s">
@@ -18011,7 +18019,7 @@
       </c>
     </row>
     <row r="196" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="3">
+      <c r="A196" s="9">
         <v>1571</v>
       </c>
       <c r="B196" s="4" t="s">
@@ -18052,7 +18060,7 @@
       </c>
     </row>
     <row r="197" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="22">
         <v>1572</v>
       </c>
       <c r="B197" s="7" t="s">
@@ -18093,7 +18101,7 @@
       </c>
     </row>
     <row r="198" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="3">
+      <c r="A198" s="9">
         <v>1573</v>
       </c>
       <c r="B198" s="4" t="s">
@@ -18134,7 +18142,7 @@
       </c>
     </row>
     <row r="199" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="3">
+      <c r="A199" s="9">
         <v>1574</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -18175,7 +18183,7 @@
       </c>
     </row>
     <row r="200" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="3">
+      <c r="A200" s="9">
         <v>1575</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -18216,7 +18224,7 @@
       </c>
     </row>
     <row r="201" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="6">
+      <c r="A201" s="22">
         <v>1576</v>
       </c>
       <c r="B201" s="7" t="s">
@@ -18257,7 +18265,7 @@
       </c>
     </row>
     <row r="202" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="3">
+      <c r="A202" s="9">
         <v>1577</v>
       </c>
       <c r="B202" s="4" t="s">
@@ -18298,7 +18306,7 @@
       </c>
     </row>
     <row r="203" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="3">
+      <c r="A203" s="9">
         <v>1578</v>
       </c>
       <c r="B203" s="4" t="s">
@@ -18339,7 +18347,7 @@
       </c>
     </row>
     <row r="204" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="3">
+      <c r="A204" s="9">
         <v>1579</v>
       </c>
       <c r="B204" s="4" t="s">
@@ -18380,7 +18388,7 @@
       </c>
     </row>
     <row r="205" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="3">
+      <c r="A205" s="9">
         <v>1580</v>
       </c>
       <c r="B205" s="4" t="s">
@@ -18421,7 +18429,7 @@
       </c>
     </row>
     <row r="206" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="3">
+      <c r="A206" s="9">
         <v>1582</v>
       </c>
       <c r="B206" s="4" t="s">
@@ -18462,7 +18470,7 @@
       </c>
     </row>
     <row r="207" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="3">
+      <c r="A207" s="9">
         <v>1583</v>
       </c>
       <c r="B207" s="4" t="s">
@@ -18503,7 +18511,7 @@
       </c>
     </row>
     <row r="208" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="3">
+      <c r="A208" s="9">
         <v>1584</v>
       </c>
       <c r="B208" s="4" t="s">
@@ -18544,7 +18552,7 @@
       </c>
     </row>
     <row r="209" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="3">
+      <c r="A209" s="9">
         <v>1585</v>
       </c>
       <c r="B209" s="4" t="s">
@@ -18585,7 +18593,7 @@
       </c>
     </row>
     <row r="210" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="3">
+      <c r="A210" s="9">
         <v>1586</v>
       </c>
       <c r="B210" s="4" t="s">
@@ -18626,7 +18634,7 @@
       </c>
     </row>
     <row r="211" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="3">
+      <c r="A211" s="9">
         <v>1587</v>
       </c>
       <c r="B211" s="4" t="s">
@@ -18667,7 +18675,7 @@
       </c>
     </row>
     <row r="212" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="3">
+      <c r="A212" s="9">
         <v>1588</v>
       </c>
       <c r="B212" s="4" t="s">
@@ -18708,7 +18716,7 @@
       </c>
     </row>
     <row r="213" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="3">
+      <c r="A213" s="9">
         <v>1589</v>
       </c>
       <c r="B213" s="4" t="s">
@@ -18749,7 +18757,7 @@
       </c>
     </row>
     <row r="214" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="3">
+      <c r="A214" s="9">
         <v>1590</v>
       </c>
       <c r="B214" s="4" t="s">
@@ -18790,7 +18798,7 @@
       </c>
     </row>
     <row r="215" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="3">
+      <c r="A215" s="9">
         <v>1592</v>
       </c>
       <c r="B215" s="4" t="s">
@@ -18831,7 +18839,7 @@
       </c>
     </row>
     <row r="216" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="6">
+      <c r="A216" s="22">
         <v>1593</v>
       </c>
       <c r="B216" s="7" t="s">
@@ -18872,7 +18880,7 @@
       </c>
     </row>
     <row r="217" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="3">
+      <c r="A217" s="9">
         <v>1595</v>
       </c>
       <c r="B217" s="4" t="s">
@@ -18913,7 +18921,7 @@
       </c>
     </row>
     <row r="218" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="3">
+      <c r="A218" s="9">
         <v>1601</v>
       </c>
       <c r="B218" s="4" t="s">
@@ -18954,7 +18962,7 @@
       </c>
     </row>
     <row r="219" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="3">
+      <c r="A219" s="9">
         <v>1610</v>
       </c>
       <c r="B219" s="4" t="s">
@@ -18995,7 +19003,7 @@
       </c>
     </row>
     <row r="220" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="3">
+      <c r="A220" s="9">
         <v>1620</v>
       </c>
       <c r="B220" s="4" t="s">
@@ -19036,7 +19044,7 @@
       </c>
     </row>
     <row r="221" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="3">
+      <c r="A221" s="9">
         <v>1622</v>
       </c>
       <c r="B221" s="4" t="s">
@@ -19077,7 +19085,7 @@
       </c>
     </row>
     <row r="222" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="3">
+      <c r="A222" s="9">
         <v>1626</v>
       </c>
       <c r="B222" s="4" t="s">
@@ -19118,7 +19126,7 @@
       </c>
     </row>
     <row r="223" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="3">
+      <c r="A223" s="9">
         <v>1630</v>
       </c>
       <c r="B223" s="4" t="s">
@@ -19159,7 +19167,7 @@
       </c>
     </row>
     <row r="224" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="3">
+      <c r="A224" s="9">
         <v>1634</v>
       </c>
       <c r="B224" s="4" t="s">
@@ -19200,7 +19208,7 @@
       </c>
     </row>
     <row r="225" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="3">
+      <c r="A225" s="9">
         <v>1636</v>
       </c>
       <c r="B225" s="4" t="s">
@@ -19241,7 +19249,7 @@
       </c>
     </row>
     <row r="226" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="3">
+      <c r="A226" s="9">
         <v>1648</v>
       </c>
       <c r="B226" s="4" t="s">
@@ -19282,7 +19290,7 @@
       </c>
     </row>
     <row r="227" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="3">
+      <c r="A227" s="9">
         <v>1652</v>
       </c>
       <c r="B227" s="4" t="s">
@@ -19323,7 +19331,7 @@
       </c>
     </row>
     <row r="228" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="3">
+      <c r="A228" s="9">
         <v>1654</v>
       </c>
       <c r="B228" s="4" t="s">
@@ -19364,7 +19372,7 @@
       </c>
     </row>
     <row r="229" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="3">
+      <c r="A229" s="9">
         <v>1660</v>
       </c>
       <c r="B229" s="4" t="s">
@@ -19405,7 +19413,7 @@
       </c>
     </row>
     <row r="230" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="3">
+      <c r="A230" s="9">
         <v>1801</v>
       </c>
       <c r="B230" s="4" t="s">
@@ -19446,7 +19454,7 @@
       </c>
     </row>
     <row r="231" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="3">
+      <c r="A231" s="9">
         <v>1803</v>
       </c>
       <c r="B231" s="4" t="s">
@@ -19487,7 +19495,7 @@
       </c>
     </row>
     <row r="232" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="3">
+      <c r="A232" s="9">
         <v>1812</v>
       </c>
       <c r="B232" s="4" t="s">
@@ -19528,7 +19536,7 @@
       </c>
     </row>
     <row r="233" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="6">
+      <c r="A233" s="22">
         <v>1820</v>
       </c>
       <c r="B233" s="7" t="s">
@@ -19569,7 +19577,7 @@
       </c>
     </row>
     <row r="234" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="6">
+      <c r="A234" s="22">
         <v>1822</v>
       </c>
       <c r="B234" s="7" t="s">
@@ -19610,7 +19618,7 @@
       </c>
     </row>
     <row r="235" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="3">
+      <c r="A235" s="9">
         <v>1825</v>
       </c>
       <c r="B235" s="4" t="s">
@@ -19651,7 +19659,7 @@
       </c>
     </row>
     <row r="236" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="3">
+      <c r="A236" s="9">
         <v>1830</v>
       </c>
       <c r="B236" s="4" t="s">
@@ -19692,7 +19700,7 @@
       </c>
     </row>
     <row r="237" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="3">
+      <c r="A237" s="9">
         <v>1832</v>
       </c>
       <c r="B237" s="4" t="s">
@@ -19733,7 +19741,7 @@
       </c>
     </row>
     <row r="238" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="3">
+      <c r="A238" s="9">
         <v>1833</v>
       </c>
       <c r="B238" s="4" t="s">
@@ -19774,7 +19782,7 @@
       </c>
     </row>
     <row r="239" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="3">
+      <c r="A239" s="9">
         <v>1834</v>
       </c>
       <c r="B239" s="4" t="s">
@@ -19815,7 +19823,7 @@
       </c>
     </row>
     <row r="240" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="3">
+      <c r="A240" s="9">
         <v>1835</v>
       </c>
       <c r="B240" s="4" t="s">
@@ -19856,7 +19864,7 @@
       </c>
     </row>
     <row r="241" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="6">
+      <c r="A241" s="22">
         <v>1840</v>
       </c>
       <c r="B241" s="7" t="s">
@@ -19897,7 +19905,7 @@
       </c>
     </row>
     <row r="242" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="3">
+      <c r="A242" s="9">
         <v>1846</v>
       </c>
       <c r="B242" s="4" t="s">
@@ -19938,7 +19946,7 @@
       </c>
     </row>
     <row r="243" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="3">
+      <c r="A243" s="9">
         <v>1850</v>
       </c>
       <c r="B243" s="9" t="s">
@@ -19979,7 +19987,7 @@
       </c>
     </row>
     <row r="244" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="3">
+      <c r="A244" s="9">
         <v>1853</v>
       </c>
       <c r="B244" s="4" t="s">
@@ -20020,7 +20028,7 @@
       </c>
     </row>
     <row r="245" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="3">
+      <c r="A245" s="9">
         <v>1855</v>
       </c>
       <c r="B245" s="4" t="s">
@@ -20061,7 +20069,7 @@
       </c>
     </row>
     <row r="246" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="3">
+      <c r="A246" s="9">
         <v>1860</v>
       </c>
       <c r="B246" s="4" t="s">
@@ -20102,7 +20110,7 @@
       </c>
     </row>
     <row r="247" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="3">
+      <c r="A247" s="9">
         <v>1861</v>
       </c>
       <c r="B247" s="4" t="s">
@@ -20143,7 +20151,7 @@
       </c>
     </row>
     <row r="248" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="3">
+      <c r="A248" s="9">
         <v>1862</v>
       </c>
       <c r="B248" s="4" t="s">
@@ -20184,7 +20192,7 @@
       </c>
     </row>
     <row r="249" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="3">
+      <c r="A249" s="9">
         <v>1865</v>
       </c>
       <c r="B249" s="4" t="s">
@@ -20225,7 +20233,7 @@
       </c>
     </row>
     <row r="250" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="3">
+      <c r="A250" s="9">
         <v>1870</v>
       </c>
       <c r="B250" s="4" t="s">
@@ -20266,7 +20274,7 @@
       </c>
     </row>
     <row r="251" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="3">
+      <c r="A251" s="9">
         <v>2101</v>
       </c>
       <c r="B251" s="4" t="s">
@@ -20307,7 +20315,7 @@
       </c>
     </row>
     <row r="252" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="3">
+      <c r="A252" s="9">
         <v>2102</v>
       </c>
       <c r="B252" s="4" t="s">
@@ -20348,7 +20356,7 @@
       </c>
     </row>
     <row r="253" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="3">
+      <c r="A253" s="9">
         <v>2103</v>
       </c>
       <c r="B253" s="4" t="s">
@@ -20389,7 +20397,7 @@
       </c>
     </row>
     <row r="254" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="3">
+      <c r="A254" s="9">
         <v>2104</v>
       </c>
       <c r="B254" s="4" t="s">
@@ -20430,7 +20438,7 @@
       </c>
     </row>
     <row r="255" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="3">
+      <c r="A255" s="9">
         <v>2105</v>
       </c>
       <c r="B255" s="4" t="s">
@@ -20471,7 +20479,7 @@
       </c>
     </row>
     <row r="256" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="3">
+      <c r="A256" s="9">
         <v>2106</v>
       </c>
       <c r="B256" s="4" t="s">
@@ -20512,7 +20520,7 @@
       </c>
     </row>
     <row r="257" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="3">
+      <c r="A257" s="9">
         <v>2107</v>
       </c>
       <c r="B257" s="4" t="s">
@@ -20553,7 +20561,7 @@
       </c>
     </row>
     <row r="258" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="3">
+      <c r="A258" s="9">
         <v>2108</v>
       </c>
       <c r="B258" s="4" t="s">
@@ -20594,7 +20602,7 @@
       </c>
     </row>
     <row r="259" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="3">
+      <c r="A259" s="9">
         <v>2109</v>
       </c>
       <c r="B259" s="4" t="s">
@@ -20635,7 +20643,7 @@
       </c>
     </row>
     <row r="260" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="3">
+      <c r="A260" s="9">
         <v>2110</v>
       </c>
       <c r="B260" s="4" t="s">
@@ -20676,7 +20684,7 @@
       </c>
     </row>
     <row r="261" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="3">
+      <c r="A261" s="9">
         <v>2111</v>
       </c>
       <c r="B261" s="4" t="s">
@@ -20717,7 +20725,7 @@
       </c>
     </row>
     <row r="262" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="3">
+      <c r="A262" s="9">
         <v>2112</v>
       </c>
       <c r="B262" s="4" t="s">
@@ -20758,7 +20766,7 @@
       </c>
     </row>
     <row r="263" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="3">
+      <c r="A263" s="9">
         <v>2114</v>
       </c>
       <c r="B263" s="4" t="s">
@@ -20799,7 +20807,7 @@
       </c>
     </row>
     <row r="264" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="3">
+      <c r="A264" s="9">
         <v>2115</v>
       </c>
       <c r="B264" s="4" t="s">
@@ -20840,7 +20848,7 @@
       </c>
     </row>
     <row r="265" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="3">
+      <c r="A265" s="9">
         <v>2116</v>
       </c>
       <c r="B265" s="4" t="s">
@@ -20881,7 +20889,7 @@
       </c>
     </row>
     <row r="266" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="3">
+      <c r="A266" s="9">
         <v>2118</v>
       </c>
       <c r="B266" s="4" t="s">
@@ -20922,7 +20930,7 @@
       </c>
     </row>
     <row r="267" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="3">
+      <c r="A267" s="9">
         <v>2120</v>
       </c>
       <c r="B267" s="4" t="s">
@@ -20963,7 +20971,7 @@
       </c>
     </row>
     <row r="268" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="3">
+      <c r="A268" s="9">
         <v>2125</v>
       </c>
       <c r="B268" s="4" t="s">
@@ -21004,7 +21012,7 @@
       </c>
     </row>
     <row r="269" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="3">
+      <c r="A269" s="9">
         <v>2126</v>
       </c>
       <c r="B269" s="4" t="s">
@@ -21045,7 +21053,7 @@
       </c>
     </row>
     <row r="270" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="6">
+      <c r="A270" s="22">
         <v>2128</v>
       </c>
       <c r="B270" s="7" t="s">
@@ -21086,7 +21094,7 @@
       </c>
     </row>
     <row r="271" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="3">
+      <c r="A271" s="9">
         <v>2132</v>
       </c>
       <c r="B271" s="4" t="s">
@@ -21127,7 +21135,7 @@
       </c>
     </row>
     <row r="272" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="3">
+      <c r="A272" s="9">
         <v>2134</v>
       </c>
       <c r="B272" s="4" t="s">
@@ -21168,7 +21176,7 @@
       </c>
     </row>
     <row r="273" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="3">
+      <c r="A273" s="9">
         <v>2139</v>
       </c>
       <c r="B273" s="4" t="s">
@@ -21209,7 +21217,7 @@
       </c>
     </row>
     <row r="274" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="3">
+      <c r="A274" s="9">
         <v>2140</v>
       </c>
       <c r="B274" s="4" t="s">
@@ -21250,7 +21258,7 @@
       </c>
     </row>
     <row r="275" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="3">
+      <c r="A275" s="9">
         <v>2165</v>
       </c>
       <c r="B275" s="4" t="s">
@@ -21291,7 +21299,7 @@
       </c>
     </row>
     <row r="276" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="3">
+      <c r="A276" s="9">
         <v>2171</v>
       </c>
       <c r="B276" s="4" t="s">
@@ -21332,7 +21340,7 @@
       </c>
     </row>
     <row r="277" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="3">
+      <c r="A277" s="9">
         <v>2172</v>
       </c>
       <c r="B277" s="4" t="s">
@@ -21373,7 +21381,7 @@
       </c>
     </row>
     <row r="278" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="3">
+      <c r="A278" s="9">
         <v>2174</v>
       </c>
       <c r="B278" s="4" t="s">
@@ -21414,7 +21422,7 @@
       </c>
     </row>
     <row r="279" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="3">
+      <c r="A279" s="9">
         <v>2175</v>
       </c>
       <c r="B279" s="4" t="s">
@@ -21455,7 +21463,7 @@
       </c>
     </row>
     <row r="280" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="3">
+      <c r="A280" s="9">
         <v>2180</v>
       </c>
       <c r="B280" s="4" t="s">
@@ -21496,7 +21504,7 @@
       </c>
     </row>
     <row r="281" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="3">
+      <c r="A281" s="9">
         <v>2401</v>
       </c>
       <c r="B281" s="4" t="s">
@@ -21537,7 +21545,7 @@
       </c>
     </row>
     <row r="282" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="3">
+      <c r="A282" s="9">
         <v>2402</v>
       </c>
       <c r="B282" s="4" t="s">
@@ -21578,7 +21586,7 @@
       </c>
     </row>
     <row r="283" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="3">
+      <c r="A283" s="9">
         <v>2403</v>
       </c>
       <c r="B283" s="4" t="s">
@@ -21619,7 +21627,7 @@
       </c>
     </row>
     <row r="284" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="3">
+      <c r="A284" s="9">
         <v>2405</v>
       </c>
       <c r="B284" s="4" t="s">
@@ -21660,7 +21668,7 @@
       </c>
     </row>
     <row r="285" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="3">
+      <c r="A285" s="9">
         <v>2408</v>
       </c>
       <c r="B285" s="4" t="s">
@@ -21701,7 +21709,7 @@
       </c>
     </row>
     <row r="286" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="3">
+      <c r="A286" s="9">
         <v>2410</v>
       </c>
       <c r="B286" s="4" t="s">
@@ -21742,7 +21750,7 @@
       </c>
     </row>
     <row r="287" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="3">
+      <c r="A287" s="9">
         <v>2412</v>
       </c>
       <c r="B287" s="4" t="s">
@@ -21783,7 +21791,7 @@
       </c>
     </row>
     <row r="288" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="3">
+      <c r="A288" s="9">
         <v>2413</v>
       </c>
       <c r="B288" s="4" t="s">
@@ -21824,7 +21832,7 @@
       </c>
     </row>
     <row r="289" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="3">
+      <c r="A289" s="9">
         <v>2414</v>
       </c>
       <c r="B289" s="4" t="s">
@@ -21865,7 +21873,7 @@
       </c>
     </row>
     <row r="290" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="3">
+      <c r="A290" s="9">
         <v>2416</v>
       </c>
       <c r="B290" s="4" t="s">
@@ -21906,7 +21914,7 @@
       </c>
     </row>
     <row r="291" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="3">
+      <c r="A291" s="9">
         <v>2420</v>
       </c>
       <c r="B291" s="4" t="s">
@@ -21947,7 +21955,7 @@
       </c>
     </row>
     <row r="292" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="6">
+      <c r="A292" s="22">
         <v>2422</v>
       </c>
       <c r="B292" s="7" t="s">
@@ -21988,7 +21996,7 @@
       </c>
     </row>
     <row r="293" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A293" s="3">
+      <c r="A293" s="9">
         <v>2427</v>
       </c>
       <c r="B293" s="4" t="s">
@@ -22029,7 +22037,7 @@
       </c>
     </row>
     <row r="294" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="3">
+      <c r="A294" s="9">
         <v>2435</v>
       </c>
       <c r="B294" s="4" t="s">
@@ -22070,7 +22078,7 @@
       </c>
     </row>
     <row r="295" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="3">
+      <c r="A295" s="9">
         <v>2437</v>
       </c>
       <c r="B295" s="4" t="s">
@@ -22111,7 +22119,7 @@
       </c>
     </row>
     <row r="296" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="3">
+      <c r="A296" s="9">
         <v>2440</v>
       </c>
       <c r="B296" s="4" t="s">
@@ -22152,7 +22160,7 @@
       </c>
     </row>
     <row r="297" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="3">
+      <c r="A297" s="9">
         <v>2442</v>
       </c>
       <c r="B297" s="4" t="s">
@@ -22193,7 +22201,7 @@
       </c>
     </row>
     <row r="298" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="3">
+      <c r="A298" s="9">
         <v>2445</v>
       </c>
       <c r="B298" s="4" t="s">
@@ -22234,7 +22242,7 @@
       </c>
     </row>
     <row r="299" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A299" s="3">
+      <c r="A299" s="9">
         <v>2455</v>
       </c>
       <c r="B299" s="4" t="s">
@@ -22275,7 +22283,7 @@
       </c>
     </row>
     <row r="300" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="3">
+      <c r="A300" s="9">
         <v>2460</v>
       </c>
       <c r="B300" s="4" t="s">
@@ -22316,7 +22324,7 @@
       </c>
     </row>
     <row r="301" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="3">
+      <c r="A301" s="9">
         <v>2465</v>
       </c>
       <c r="B301" s="4" t="s">
@@ -22357,7 +22365,7 @@
       </c>
     </row>
     <row r="302" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="3">
+      <c r="A302" s="9">
         <v>2470</v>
       </c>
       <c r="B302" s="4" t="s">
@@ -22398,7 +22406,7 @@
       </c>
     </row>
     <row r="303" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="3">
+      <c r="A303" s="9">
         <v>2701</v>
       </c>
       <c r="B303" s="4" t="s">
@@ -22439,7 +22447,7 @@
       </c>
     </row>
     <row r="304" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="3">
+      <c r="A304" s="9">
         <v>2703</v>
       </c>
       <c r="B304" s="4" t="s">
@@ -22480,7 +22488,7 @@
       </c>
     </row>
     <row r="305" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="6">
+      <c r="A305" s="22">
         <v>2712</v>
       </c>
       <c r="B305" s="7" t="s">
@@ -22521,7 +22529,7 @@
       </c>
     </row>
     <row r="306" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A306" s="3">
+      <c r="A306" s="9">
         <v>2715</v>
       </c>
       <c r="B306" s="4" t="s">
@@ -22562,7 +22570,7 @@
       </c>
     </row>
     <row r="307" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="3">
+      <c r="A307" s="9">
         <v>2717</v>
       </c>
       <c r="B307" s="4" t="s">
@@ -22603,7 +22611,7 @@
       </c>
     </row>
     <row r="308" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A308" s="3">
+      <c r="A308" s="9">
         <v>2719</v>
       </c>
       <c r="B308" s="4" t="s">
@@ -22644,7 +22652,7 @@
       </c>
     </row>
     <row r="309" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="3">
+      <c r="A309" s="9">
         <v>2721</v>
       </c>
       <c r="B309" s="4" t="s">
@@ -22685,7 +22693,7 @@
       </c>
     </row>
     <row r="310" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="3">
+      <c r="A310" s="9">
         <v>2730</v>
       </c>
       <c r="B310" s="4" t="s">
@@ -22726,7 +22734,7 @@
       </c>
     </row>
     <row r="311" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="3">
+      <c r="A311" s="9">
         <v>2745</v>
       </c>
       <c r="B311" s="4" t="s">
@@ -22767,7 +22775,7 @@
       </c>
     </row>
     <row r="312" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A312" s="3">
+      <c r="A312" s="9">
         <v>2747</v>
       </c>
       <c r="B312" s="4" t="s">
@@ -22808,7 +22816,7 @@
       </c>
     </row>
     <row r="313" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="3">
+      <c r="A313" s="9">
         <v>2750</v>
       </c>
       <c r="B313" s="4" t="s">
@@ -22849,7 +22857,7 @@
       </c>
     </row>
     <row r="314" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A314" s="3">
+      <c r="A314" s="9">
         <v>2752</v>
       </c>
       <c r="B314" s="4" t="s">
@@ -22890,7 +22898,7 @@
       </c>
     </row>
     <row r="315" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="3">
+      <c r="A315" s="9">
         <v>2754</v>
       </c>
       <c r="B315" s="4" t="s">
@@ -22931,7 +22939,7 @@
       </c>
     </row>
     <row r="316" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A316" s="3">
+      <c r="A316" s="9">
         <v>2757</v>
       </c>
       <c r="B316" s="4" t="s">
@@ -22972,7 +22980,7 @@
       </c>
     </row>
     <row r="317" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A317" s="3">
+      <c r="A317" s="9">
         <v>2765</v>
       </c>
       <c r="B317" s="4" t="s">
@@ -23013,7 +23021,7 @@
       </c>
     </row>
     <row r="318" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A318" s="3">
+      <c r="A318" s="9">
         <v>2767</v>
       </c>
       <c r="B318" s="4" t="s">
@@ -23054,7 +23062,7 @@
       </c>
     </row>
     <row r="319" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A319" s="6">
+      <c r="A319" s="22">
         <v>2769</v>
       </c>
       <c r="B319" s="7" t="s">
@@ -23095,7 +23103,7 @@
       </c>
     </row>
     <row r="320" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="3">
+      <c r="A320" s="9">
         <v>2770</v>
       </c>
       <c r="B320" s="4" t="s">
@@ -23136,7 +23144,7 @@
       </c>
     </row>
     <row r="321" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="6">
+      <c r="A321" s="22">
         <v>2771</v>
       </c>
       <c r="B321" s="7" t="s">
@@ -23177,7 +23185,7 @@
       </c>
     </row>
     <row r="322" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A322" s="6">
+      <c r="A322" s="22">
         <v>2772</v>
       </c>
       <c r="B322" s="7" t="s">
@@ -23218,7 +23226,7 @@
       </c>
     </row>
     <row r="323" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A323" s="3">
+      <c r="A323" s="9">
         <v>2773</v>
       </c>
       <c r="B323" s="4" t="s">
@@ -23259,7 +23267,7 @@
       </c>
     </row>
     <row r="324" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="3">
+      <c r="A324" s="9">
         <v>2775</v>
       </c>
       <c r="B324" s="4" t="s">
@@ -23300,7 +23308,7 @@
       </c>
     </row>
     <row r="325" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="3">
+      <c r="A325" s="9">
         <v>2777</v>
       </c>
       <c r="B325" s="4" t="s">
@@ -23341,7 +23349,7 @@
       </c>
     </row>
     <row r="326" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A326" s="3">
+      <c r="A326" s="9">
         <v>2780</v>
       </c>
       <c r="B326" s="4" t="s">
@@ -23382,7 +23390,7 @@
       </c>
     </row>
     <row r="327" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A327" s="6">
+      <c r="A327" s="22">
         <v>2786</v>
       </c>
       <c r="B327" s="7" t="s">
@@ -23423,7 +23431,7 @@
       </c>
     </row>
     <row r="328" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="3">
+      <c r="A328" s="9">
         <v>2790</v>
       </c>
       <c r="B328" s="4" t="s">
@@ -23462,7 +23470,7 @@
       <c r="M328" s="4"/>
     </row>
     <row r="329" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A329" s="3">
+      <c r="A329" s="9">
         <v>3101</v>
       </c>
       <c r="B329" s="4" t="s">
@@ -23503,7 +23511,7 @@
       </c>
     </row>
     <row r="330" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="3">
+      <c r="A330" s="9">
         <v>3105</v>
       </c>
       <c r="B330" s="4" t="s">
@@ -23544,7 +23552,7 @@
       </c>
     </row>
     <row r="331" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="3">
+      <c r="A331" s="9">
         <v>3106</v>
       </c>
       <c r="B331" s="4" t="s">
@@ -23585,7 +23593,7 @@
       </c>
     </row>
     <row r="332" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="3">
+      <c r="A332" s="9">
         <v>3107</v>
       </c>
       <c r="B332" s="4" t="s">
@@ -23626,7 +23634,7 @@
       </c>
     </row>
     <row r="333" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A333" s="3">
+      <c r="A333" s="9">
         <v>3109</v>
       </c>
       <c r="B333" s="4" t="s">
@@ -23667,7 +23675,7 @@
       </c>
     </row>
     <row r="334" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="3">
+      <c r="A334" s="9">
         <v>3110</v>
       </c>
       <c r="B334" s="4" t="s">
@@ -23708,7 +23716,7 @@
       </c>
     </row>
     <row r="335" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="3">
+      <c r="A335" s="9">
         <v>3111</v>
       </c>
       <c r="B335" s="4" t="s">
@@ -23749,7 +23757,7 @@
       </c>
     </row>
     <row r="336" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="6">
+      <c r="A336" s="22">
         <v>3113</v>
       </c>
       <c r="B336" s="7" t="s">
@@ -23790,7 +23798,7 @@
       </c>
     </row>
     <row r="337" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A337" s="3">
+      <c r="A337" s="9">
         <v>3114</v>
       </c>
       <c r="B337" s="4" t="s">
@@ -23831,7 +23839,7 @@
       </c>
     </row>
     <row r="338" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A338" s="3">
+      <c r="A338" s="9">
         <v>3115</v>
       </c>
       <c r="B338" s="4" t="s">
@@ -23872,7 +23880,7 @@
       </c>
     </row>
     <row r="339" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="3">
+      <c r="A339" s="9">
         <v>3116</v>
       </c>
       <c r="B339" s="4" t="s">
@@ -23913,7 +23921,7 @@
       </c>
     </row>
     <row r="340" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="3">
+      <c r="A340" s="9">
         <v>3117</v>
       </c>
       <c r="B340" s="4" t="s">
@@ -23954,7 +23962,7 @@
       </c>
     </row>
     <row r="341" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="3">
+      <c r="A341" s="9">
         <v>3118</v>
       </c>
       <c r="B341" s="4" t="s">
@@ -23995,7 +24003,7 @@
       </c>
     </row>
     <row r="342" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="3">
+      <c r="A342" s="9">
         <v>3120</v>
       </c>
       <c r="B342" s="4" t="s">
@@ -24036,7 +24044,7 @@
       </c>
     </row>
     <row r="343" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="3">
+      <c r="A343" s="9">
         <v>3121</v>
       </c>
       <c r="B343" s="4" t="s">
@@ -24077,7 +24085,7 @@
       </c>
     </row>
     <row r="344" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="3">
+      <c r="A344" s="9">
         <v>3122</v>
       </c>
       <c r="B344" s="4" t="s">
@@ -24118,7 +24126,7 @@
       </c>
     </row>
     <row r="345" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="3">
+      <c r="A345" s="9">
         <v>3123</v>
       </c>
       <c r="B345" s="4" t="s">
@@ -24159,7 +24167,7 @@
       </c>
     </row>
     <row r="346" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="3">
+      <c r="A346" s="9">
         <v>3124</v>
       </c>
       <c r="B346" s="4" t="s">
@@ -24200,7 +24208,7 @@
       </c>
     </row>
     <row r="347" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="3">
+      <c r="A347" s="9">
         <v>3126</v>
       </c>
       <c r="B347" s="4" t="s">
@@ -24241,7 +24249,7 @@
       </c>
     </row>
     <row r="348" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="3">
+      <c r="A348" s="9">
         <v>3127</v>
       </c>
       <c r="B348" s="4" t="s">
@@ -24282,7 +24290,7 @@
       </c>
     </row>
     <row r="349" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="6">
+      <c r="A349" s="22">
         <v>3130</v>
       </c>
       <c r="B349" s="7" t="s">
@@ -24323,7 +24331,7 @@
       </c>
     </row>
     <row r="350" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="3">
+      <c r="A350" s="9">
         <v>3133</v>
       </c>
       <c r="B350" s="4" t="s">
@@ -24364,7 +24372,7 @@
       </c>
     </row>
     <row r="351" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="3">
+      <c r="A351" s="9">
         <v>3134</v>
       </c>
       <c r="B351" s="4" t="s">
@@ -24405,7 +24413,7 @@
       </c>
     </row>
     <row r="352" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="3">
+      <c r="A352" s="9">
         <v>3135</v>
       </c>
       <c r="B352" s="4" t="s">
@@ -24446,7 +24454,7 @@
       </c>
     </row>
     <row r="353" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="3">
+      <c r="A353" s="9">
         <v>3136</v>
       </c>
       <c r="B353" s="4" t="s">
@@ -24487,7 +24495,7 @@
       </c>
     </row>
     <row r="354" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="3">
+      <c r="A354" s="9">
         <v>3137</v>
       </c>
       <c r="B354" s="4" t="s">
@@ -24528,7 +24536,7 @@
       </c>
     </row>
     <row r="355" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="3">
+      <c r="A355" s="9">
         <v>3138</v>
       </c>
       <c r="B355" s="4" t="s">
@@ -24569,7 +24577,7 @@
       </c>
     </row>
     <row r="356" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="3">
+      <c r="A356" s="9">
         <v>3139</v>
       </c>
       <c r="B356" s="4" t="s">
@@ -24610,7 +24618,7 @@
       </c>
     </row>
     <row r="357" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="3">
+      <c r="A357" s="9">
         <v>3140</v>
       </c>
       <c r="B357" s="4" t="s">
@@ -24651,7 +24659,7 @@
       </c>
     </row>
     <row r="358" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A358" s="3">
+      <c r="A358" s="9">
         <v>3141</v>
       </c>
       <c r="B358" s="4" t="s">
@@ -24692,7 +24700,7 @@
       </c>
     </row>
     <row r="359" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A359" s="3">
+      <c r="A359" s="9">
         <v>3142</v>
       </c>
       <c r="B359" s="4" t="s">
@@ -24733,7 +24741,7 @@
       </c>
     </row>
     <row r="360" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A360" s="3">
+      <c r="A360" s="9">
         <v>3143</v>
       </c>
       <c r="B360" s="4" t="s">
@@ -24774,7 +24782,7 @@
       </c>
     </row>
     <row r="361" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="3">
+      <c r="A361" s="9">
         <v>3144</v>
       </c>
       <c r="B361" s="4" t="s">
@@ -24815,7 +24823,7 @@
       </c>
     </row>
     <row r="362" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A362" s="3">
+      <c r="A362" s="9">
         <v>3145</v>
       </c>
       <c r="B362" s="4" t="s">
@@ -24856,7 +24864,7 @@
       </c>
     </row>
     <row r="363" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="3">
+      <c r="A363" s="9">
         <v>3146</v>
       </c>
       <c r="B363" s="4" t="s">
@@ -24897,7 +24905,7 @@
       </c>
     </row>
     <row r="364" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="3">
+      <c r="A364" s="9">
         <v>3147</v>
       </c>
       <c r="B364" s="4" t="s">
@@ -24938,7 +24946,7 @@
       </c>
     </row>
     <row r="365" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="3">
+      <c r="A365" s="9">
         <v>3148</v>
       </c>
       <c r="B365" s="4" t="s">
@@ -24979,7 +24987,7 @@
       </c>
     </row>
     <row r="366" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="3">
+      <c r="A366" s="9">
         <v>3149</v>
       </c>
       <c r="B366" s="4" t="s">
@@ -25020,7 +25028,7 @@
       </c>
     </row>
     <row r="367" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="3">
+      <c r="A367" s="9">
         <v>3150</v>
       </c>
       <c r="B367" s="4" t="s">
@@ -25061,7 +25069,7 @@
       </c>
     </row>
     <row r="368" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="3">
+      <c r="A368" s="9">
         <v>3152</v>
       </c>
       <c r="B368" s="4" t="s">
@@ -25102,7 +25110,7 @@
       </c>
     </row>
     <row r="369" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="3">
+      <c r="A369" s="9">
         <v>3153</v>
       </c>
       <c r="B369" s="4" t="s">
@@ -25143,7 +25151,7 @@
       </c>
     </row>
     <row r="370" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="3">
+      <c r="A370" s="9">
         <v>3154</v>
       </c>
       <c r="B370" s="4" t="s">
@@ -25184,7 +25192,7 @@
       </c>
     </row>
     <row r="371" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="3">
+      <c r="A371" s="9">
         <v>3155</v>
       </c>
       <c r="B371" s="4" t="s">
@@ -25225,7 +25233,7 @@
       </c>
     </row>
     <row r="372" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="3">
+      <c r="A372" s="9">
         <v>3156</v>
       </c>
       <c r="B372" s="4" t="s">
@@ -25266,7 +25274,7 @@
       </c>
     </row>
     <row r="373" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="3">
+      <c r="A373" s="9">
         <v>3157</v>
       </c>
       <c r="B373" s="4" t="s">
@@ -25307,7 +25315,7 @@
       </c>
     </row>
     <row r="374" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="3">
+      <c r="A374" s="9">
         <v>3158</v>
       </c>
       <c r="B374" s="4" t="s">
@@ -25348,7 +25356,7 @@
       </c>
     </row>
     <row r="375" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="3">
+      <c r="A375" s="9">
         <v>3159</v>
       </c>
       <c r="B375" s="4" t="s">
@@ -25389,7 +25397,7 @@
       </c>
     </row>
     <row r="376" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A376" s="3">
+      <c r="A376" s="9">
         <v>3160</v>
       </c>
       <c r="B376" s="4" t="s">
@@ -25430,7 +25438,7 @@
       </c>
     </row>
     <row r="377" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="3">
+      <c r="A377" s="9">
         <v>3161</v>
       </c>
       <c r="B377" s="4" t="s">
@@ -25471,7 +25479,7 @@
       </c>
     </row>
     <row r="378" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="3">
+      <c r="A378" s="9">
         <v>3162</v>
       </c>
       <c r="B378" s="4" t="s">
@@ -25512,7 +25520,7 @@
       </c>
     </row>
     <row r="379" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A379" s="3">
+      <c r="A379" s="9">
         <v>3163</v>
       </c>
       <c r="B379" s="4" t="s">
@@ -25553,7 +25561,7 @@
       </c>
     </row>
     <row r="380" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A380" s="6">
+      <c r="A380" s="22">
         <v>3164</v>
       </c>
       <c r="B380" s="7" t="s">
@@ -25594,7 +25602,7 @@
       </c>
     </row>
     <row r="381" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="3">
+      <c r="A381" s="9">
         <v>3165</v>
       </c>
       <c r="B381" s="4" t="s">
@@ -25635,7 +25643,7 @@
       </c>
     </row>
     <row r="382" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="3">
+      <c r="A382" s="9">
         <v>3166</v>
       </c>
       <c r="B382" s="4" t="s">
@@ -25676,7 +25684,7 @@
       </c>
     </row>
     <row r="383" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A383" s="3">
+      <c r="A383" s="9">
         <v>3167</v>
       </c>
       <c r="B383" s="4" t="s">
@@ -25717,7 +25725,7 @@
       </c>
     </row>
     <row r="384" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A384" s="3">
+      <c r="A384" s="9">
         <v>3168</v>
       </c>
       <c r="B384" s="4" t="s">
@@ -25758,7 +25766,7 @@
       </c>
     </row>
     <row r="385" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="3">
+      <c r="A385" s="9">
         <v>3172</v>
       </c>
       <c r="B385" s="4" t="s">
@@ -25799,7 +25807,7 @@
       </c>
     </row>
     <row r="386" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="3">
+      <c r="A386" s="9">
         <v>3174</v>
       </c>
       <c r="B386" s="4" t="s">
@@ -25840,7 +25848,7 @@
       </c>
     </row>
     <row r="387" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A387" s="3">
+      <c r="A387" s="9">
         <v>3176</v>
       </c>
       <c r="B387" s="4" t="s">
@@ -25881,7 +25889,7 @@
       </c>
     </row>
     <row r="388" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A388" s="3">
+      <c r="A388" s="9">
         <v>3178</v>
       </c>
       <c r="B388" s="4" t="s">
@@ -25922,7 +25930,7 @@
       </c>
     </row>
     <row r="389" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A389" s="3">
+      <c r="A389" s="9">
         <v>3180</v>
       </c>
       <c r="B389" s="4" t="s">
@@ -25963,7 +25971,7 @@
       </c>
     </row>
     <row r="390" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A390" s="3">
+      <c r="A390" s="9">
         <v>3186</v>
       </c>
       <c r="B390" s="4" t="s">
@@ -26004,7 +26012,7 @@
       </c>
     </row>
     <row r="391" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A391" s="3">
+      <c r="A391" s="9">
         <v>3190</v>
       </c>
       <c r="B391" s="4" t="s">
@@ -26045,7 +26053,7 @@
       </c>
     </row>
     <row r="392" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A392" s="3">
+      <c r="A392" s="9">
         <v>3192</v>
       </c>
       <c r="B392" s="4" t="s">
@@ -26086,7 +26094,7 @@
       </c>
     </row>
     <row r="393" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="3">
+      <c r="A393" s="9">
         <v>3195</v>
       </c>
       <c r="B393" s="4" t="s">
@@ -26127,7 +26135,7 @@
       </c>
     </row>
     <row r="394" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A394" s="3">
+      <c r="A394" s="9">
         <v>3301</v>
       </c>
       <c r="B394" s="4" t="s">
@@ -26168,7 +26176,7 @@
       </c>
     </row>
     <row r="395" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="3">
+      <c r="A395" s="9">
         <v>3303</v>
       </c>
       <c r="B395" s="4" t="s">
@@ -26209,7 +26217,7 @@
       </c>
     </row>
     <row r="396" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A396" s="3">
+      <c r="A396" s="9">
         <v>3309</v>
       </c>
       <c r="B396" s="4" t="s">
@@ -26250,7 +26258,7 @@
       </c>
     </row>
     <row r="397" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A397" s="3">
+      <c r="A397" s="9">
         <v>3315</v>
       </c>
       <c r="B397" s="4" t="s">
@@ -26291,7 +26299,7 @@
       </c>
     </row>
     <row r="398" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="3">
+      <c r="A398" s="9">
         <v>3320</v>
       </c>
       <c r="B398" s="4" t="s">
@@ -26332,7 +26340,7 @@
       </c>
     </row>
     <row r="399" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A399" s="3">
+      <c r="A399" s="9">
         <v>3350</v>
       </c>
       <c r="B399" s="4" t="s">
@@ -26373,7 +26381,7 @@
       </c>
     </row>
     <row r="400" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="3">
+      <c r="A400" s="9">
         <v>3360</v>
       </c>
       <c r="B400" s="4" t="s">
@@ -26414,7 +26422,7 @@
       </c>
     </row>
     <row r="401" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A401" s="3">
+      <c r="A401" s="9">
         <v>3370</v>
       </c>
       <c r="B401" s="4" t="s">
@@ -26455,7 +26463,7 @@
       </c>
     </row>
     <row r="402" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A402" s="3">
+      <c r="A402" s="9">
         <v>3375</v>
       </c>
       <c r="B402" s="4" t="s">
@@ -26496,7 +26504,7 @@
       </c>
     </row>
     <row r="403" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A403" s="3">
+      <c r="A403" s="9">
         <v>3603</v>
       </c>
       <c r="B403" s="4" t="s">
@@ -26537,7 +26545,7 @@
       </c>
     </row>
     <row r="404" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A404" s="3">
+      <c r="A404" s="9">
         <v>3620</v>
       </c>
       <c r="B404" s="4" t="s">
@@ -26578,7 +26586,7 @@
       </c>
     </row>
     <row r="405" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A405" s="3">
+      <c r="A405" s="9">
         <v>3630</v>
       </c>
       <c r="B405" s="4" t="s">
@@ -26619,7 +26627,7 @@
       </c>
     </row>
     <row r="406" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A406" s="3">
+      <c r="A406" s="9">
         <v>3640</v>
       </c>
       <c r="B406" s="4" t="s">
@@ -26660,7 +26668,7 @@
       </c>
     </row>
     <row r="407" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A407" s="3">
+      <c r="A407" s="9">
         <v>3655</v>
       </c>
       <c r="B407" s="4" t="s">
@@ -26701,7 +26709,7 @@
       </c>
     </row>
     <row r="408" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="3">
+      <c r="A408" s="9">
         <v>3660</v>
       </c>
       <c r="B408" s="4" t="s">
@@ -26742,7 +26750,7 @@
       </c>
     </row>
     <row r="409" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A409" s="6">
+      <c r="A409" s="22">
         <v>3901</v>
       </c>
       <c r="B409" s="7" t="s">
@@ -26783,7 +26791,7 @@
       </c>
     </row>
     <row r="410" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A410" s="3">
+      <c r="A410" s="9">
         <v>3902</v>
       </c>
       <c r="B410" s="4" t="s">
@@ -26824,7 +26832,7 @@
       </c>
     </row>
     <row r="411" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A411" s="3">
+      <c r="A411" s="9">
         <v>3903</v>
       </c>
       <c r="B411" s="4" t="s">
@@ -26865,7 +26873,7 @@
       </c>
     </row>
     <row r="412" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A412" s="3">
+      <c r="A412" s="9">
         <v>3904</v>
       </c>
       <c r="B412" s="4" t="s">
@@ -26906,7 +26914,7 @@
       </c>
     </row>
     <row r="413" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A413" s="3">
+      <c r="A413" s="9">
         <v>3905</v>
       </c>
       <c r="B413" s="4" t="s">
@@ -26947,7 +26955,7 @@
       </c>
     </row>
     <row r="414" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A414" s="3">
+      <c r="A414" s="9">
         <v>3908</v>
       </c>
       <c r="B414" s="4" t="s">
@@ -26988,7 +26996,7 @@
       </c>
     </row>
     <row r="415" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A415" s="3">
+      <c r="A415" s="9">
         <v>3909</v>
       </c>
       <c r="B415" s="4" t="s">
@@ -27029,7 +27037,7 @@
       </c>
     </row>
     <row r="416" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A416" s="3">
+      <c r="A416" s="9">
         <v>3910</v>
       </c>
       <c r="B416" s="4" t="s">
@@ -27070,7 +27078,7 @@
       </c>
     </row>
     <row r="417" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A417" s="3">
+      <c r="A417" s="9">
         <v>3912</v>
       </c>
       <c r="B417" s="4" t="s">
@@ -27111,7 +27119,7 @@
       </c>
     </row>
     <row r="418" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A418" s="3">
+      <c r="A418" s="9">
         <v>3913</v>
       </c>
       <c r="B418" s="4" t="s">
@@ -27152,7 +27160,7 @@
       </c>
     </row>
     <row r="419" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A419" s="3">
+      <c r="A419" s="9">
         <v>3914</v>
       </c>
       <c r="B419" s="4" t="s">
@@ -27193,7 +27201,7 @@
       </c>
     </row>
     <row r="420" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A420" s="3">
+      <c r="A420" s="9">
         <v>3915</v>
       </c>
       <c r="B420" s="4" t="s">
@@ -27234,7 +27242,7 @@
       </c>
     </row>
     <row r="421" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A421" s="3">
+      <c r="A421" s="9">
         <v>3916</v>
       </c>
       <c r="B421" s="14" t="s">
@@ -27275,7 +27283,7 @@
       </c>
     </row>
     <row r="422" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="6">
+      <c r="A422" s="22">
         <v>3918</v>
       </c>
       <c r="B422" s="7" t="s">
@@ -27316,7 +27324,7 @@
       </c>
     </row>
     <row r="423" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A423" s="6">
+      <c r="A423" s="22">
         <v>3920</v>
       </c>
       <c r="B423" s="7" t="s">
@@ -27357,7 +27365,7 @@
       </c>
     </row>
     <row r="424" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A424" s="3">
+      <c r="A424" s="9">
         <v>3921</v>
       </c>
       <c r="B424" s="4" t="s">
@@ -27398,7 +27406,7 @@
       </c>
     </row>
     <row r="425" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A425" s="3">
+      <c r="A425" s="9">
         <v>3922</v>
       </c>
       <c r="B425" s="4" t="s">
@@ -27439,7 +27447,7 @@
       </c>
     </row>
     <row r="426" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A426" s="3">
+      <c r="A426" s="9">
         <v>3923</v>
       </c>
       <c r="B426" s="4" t="s">
@@ -27480,7 +27488,7 @@
       </c>
     </row>
     <row r="427" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A427" s="3">
+      <c r="A427" s="9">
         <v>3925</v>
       </c>
       <c r="B427" s="4" t="s">
@@ -27521,7 +27529,7 @@
       </c>
     </row>
     <row r="428" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A428" s="3">
+      <c r="A428" s="9">
         <v>3927</v>
       </c>
       <c r="B428" s="4" t="s">
@@ -27562,7 +27570,7 @@
       </c>
     </row>
     <row r="429" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A429" s="3">
+      <c r="A429" s="9">
         <v>3928</v>
       </c>
       <c r="B429" s="4" t="s">
@@ -27603,7 +27611,7 @@
       </c>
     </row>
     <row r="430" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A430" s="3">
+      <c r="A430" s="9">
         <v>3930</v>
       </c>
       <c r="B430" s="4" t="s">
@@ -27644,7 +27652,7 @@
       </c>
     </row>
     <row r="431" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A431" s="3">
+      <c r="A431" s="9">
         <v>3932</v>
       </c>
       <c r="B431" s="4" t="s">
@@ -27685,7 +27693,7 @@
       </c>
     </row>
     <row r="432" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A432" s="3">
+      <c r="A432" s="9">
         <v>3935</v>
       </c>
       <c r="B432" s="4" t="s">
@@ -27726,7 +27734,7 @@
       </c>
     </row>
     <row r="433" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A433" s="3">
+      <c r="A433" s="9">
         <v>3937</v>
       </c>
       <c r="B433" s="4" t="s">
@@ -27767,7 +27775,7 @@
       </c>
     </row>
     <row r="434" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A434" s="6">
+      <c r="A434" s="22">
         <v>3940</v>
       </c>
       <c r="B434" s="7" t="s">
@@ -27808,7 +27816,7 @@
       </c>
     </row>
     <row r="435" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A435" s="3">
+      <c r="A435" s="9">
         <v>3942</v>
       </c>
       <c r="B435" s="4" t="s">
@@ -27849,7 +27857,7 @@
       </c>
     </row>
     <row r="436" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A436" s="3">
+      <c r="A436" s="9">
         <v>3943</v>
       </c>
       <c r="B436" s="4" t="s">
@@ -27890,7 +27898,7 @@
       </c>
     </row>
     <row r="437" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A437" s="3">
+      <c r="A437" s="9">
         <v>3945</v>
       </c>
       <c r="B437" s="4" t="s">
@@ -27931,7 +27939,7 @@
       </c>
     </row>
     <row r="438" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A438" s="3">
+      <c r="A438" s="9">
         <v>3947</v>
       </c>
       <c r="B438" s="4" t="s">
@@ -27972,7 +27980,7 @@
       </c>
     </row>
     <row r="439" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A439" s="3">
+      <c r="A439" s="9">
         <v>3950</v>
       </c>
       <c r="B439" s="4" t="s">
@@ -28013,7 +28021,7 @@
       </c>
     </row>
     <row r="440" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A440" s="3">
+      <c r="A440" s="9">
         <v>3952</v>
       </c>
       <c r="B440" s="4" t="s">
@@ -28054,7 +28062,7 @@
       </c>
     </row>
     <row r="441" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A441" s="3">
+      <c r="A441" s="9">
         <v>3955</v>
       </c>
       <c r="B441" s="4" t="s">
@@ -28095,7 +28103,7 @@
       </c>
     </row>
     <row r="442" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A442" s="3">
+      <c r="A442" s="9">
         <v>3957</v>
       </c>
       <c r="B442" s="4" t="s">
@@ -28136,7 +28144,7 @@
       </c>
     </row>
     <row r="443" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A443" s="3">
+      <c r="A443" s="9">
         <v>3960</v>
       </c>
       <c r="B443" s="4" t="s">
@@ -28177,7 +28185,7 @@
       </c>
     </row>
     <row r="444" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A444" s="3">
+      <c r="A444" s="9">
         <v>3963</v>
       </c>
       <c r="B444" s="4" t="s">
@@ -28218,7 +28226,7 @@
       </c>
     </row>
     <row r="445" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A445" s="3">
+      <c r="A445" s="9">
         <v>3965</v>
       </c>
       <c r="B445" s="4" t="s">
@@ -28259,7 +28267,7 @@
       </c>
     </row>
     <row r="446" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A446" s="3">
+      <c r="A446" s="9">
         <v>3967</v>
       </c>
       <c r="B446" s="4" t="s">
@@ -28300,7 +28308,7 @@
       </c>
     </row>
     <row r="447" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A447" s="3">
+      <c r="A447" s="9">
         <v>3970</v>
       </c>
       <c r="B447" s="4" t="s">
@@ -28341,7 +28349,7 @@
       </c>
     </row>
     <row r="448" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A448" s="3">
+      <c r="A448" s="9">
         <v>3973</v>
       </c>
       <c r="B448" s="4" t="s">
@@ -28382,7 +28390,7 @@
       </c>
     </row>
     <row r="449" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A449" s="3">
+      <c r="A449" s="9">
         <v>3980</v>
       </c>
       <c r="B449" s="4" t="s">
@@ -28423,7 +28431,7 @@
       </c>
     </row>
     <row r="450" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A450" s="3">
+      <c r="A450" s="9">
         <v>4203</v>
       </c>
       <c r="B450" s="4" t="s">
@@ -28464,7 +28472,7 @@
       </c>
     </row>
     <row r="451" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A451" s="3">
+      <c r="A451" s="9">
         <v>4205</v>
       </c>
       <c r="B451" s="4" t="s">
@@ -28505,7 +28513,7 @@
       </c>
     </row>
     <row r="452" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A452" s="3">
+      <c r="A452" s="9">
         <v>4209</v>
       </c>
       <c r="B452" s="4" t="s">
@@ -28546,7 +28554,7 @@
       </c>
     </row>
     <row r="453" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A453" s="3">
+      <c r="A453" s="9">
         <v>4210</v>
       </c>
       <c r="B453" s="4" t="s">
@@ -28587,7 +28595,7 @@
       </c>
     </row>
     <row r="454" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A454" s="3">
+      <c r="A454" s="9">
         <v>4212</v>
       </c>
       <c r="B454" s="4" t="s">
@@ -28628,7 +28636,7 @@
       </c>
     </row>
     <row r="455" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A455" s="3">
+      <c r="A455" s="9">
         <v>4215</v>
       </c>
       <c r="B455" s="4" t="s">
@@ -28669,7 +28677,7 @@
       </c>
     </row>
     <row r="456" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A456" s="3">
+      <c r="A456" s="9">
         <v>4220</v>
       </c>
       <c r="B456" s="4" t="s">
@@ -28710,7 +28718,7 @@
       </c>
     </row>
     <row r="457" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A457" s="6">
+      <c r="A457" s="22">
         <v>4223</v>
       </c>
       <c r="B457" s="7" t="s">
@@ -28751,7 +28759,7 @@
       </c>
     </row>
     <row r="458" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A458" s="3">
+      <c r="A458" s="9">
         <v>4230</v>
       </c>
       <c r="B458" s="4" t="s">
@@ -28792,7 +28800,7 @@
       </c>
     </row>
     <row r="459" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A459" s="3">
+      <c r="A459" s="9">
         <v>4240</v>
       </c>
       <c r="B459" s="4" t="s">
@@ -28833,7 +28841,7 @@
       </c>
     </row>
     <row r="460" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="3">
+      <c r="A460" s="9">
         <v>4244</v>
       </c>
       <c r="B460" s="4" t="s">
@@ -28874,7 +28882,7 @@
       </c>
     </row>
     <row r="461" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="3">
+      <c r="A461" s="9">
         <v>4260</v>
       </c>
       <c r="B461" s="4" t="s">
@@ -28915,7 +28923,7 @@
       </c>
     </row>
     <row r="462" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A462" s="3">
+      <c r="A462" s="9">
         <v>4263</v>
       </c>
       <c r="B462" s="4" t="s">
@@ -28956,7 +28964,7 @@
       </c>
     </row>
     <row r="463" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A463" s="3">
+      <c r="A463" s="9">
         <v>4501</v>
       </c>
       <c r="B463" s="4" t="s">
@@ -28997,7 +29005,7 @@
       </c>
     </row>
     <row r="464" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A464" s="3">
+      <c r="A464" s="9">
         <v>4503</v>
       </c>
       <c r="B464" s="4" t="s">
@@ -29038,7 +29046,7 @@
       </c>
     </row>
     <row r="465" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A465" s="3">
+      <c r="A465" s="9">
         <v>4505</v>
       </c>
       <c r="B465" s="4" t="s">
@@ -29079,7 +29087,7 @@
       </c>
     </row>
     <row r="466" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A466" s="3">
+      <c r="A466" s="9">
         <v>4507</v>
       </c>
       <c r="B466" s="4" t="s">
@@ -29120,7 +29128,7 @@
       </c>
     </row>
     <row r="467" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A467" s="6">
+      <c r="A467" s="22">
         <v>4509</v>
       </c>
       <c r="B467" s="7" t="s">
@@ -29161,7 +29169,7 @@
       </c>
     </row>
     <row r="468" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A468" s="3">
+      <c r="A468" s="9">
         <v>4510</v>
       </c>
       <c r="B468" s="4" t="s">
@@ -29202,7 +29210,7 @@
       </c>
     </row>
     <row r="469" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A469" s="3">
+      <c r="A469" s="9">
         <v>4512</v>
       </c>
       <c r="B469" s="4" t="s">
@@ -29243,7 +29251,7 @@
       </c>
     </row>
     <row r="470" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A470" s="3">
+      <c r="A470" s="9">
         <v>4514</v>
       </c>
       <c r="B470" s="4" t="s">
@@ -29284,7 +29292,7 @@
       </c>
     </row>
     <row r="471" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A471" s="3">
+      <c r="A471" s="9">
         <v>4515</v>
       </c>
       <c r="B471" s="4" t="s">
@@ -29325,7 +29333,7 @@
       </c>
     </row>
     <row r="472" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A472" s="3">
+      <c r="A472" s="9">
         <v>4517</v>
       </c>
       <c r="B472" s="4" t="s">
@@ -29366,7 +29374,7 @@
       </c>
     </row>
     <row r="473" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A473" s="3">
+      <c r="A473" s="9">
         <v>4518</v>
       </c>
       <c r="B473" s="4" t="s">
@@ -29407,7 +29415,7 @@
       </c>
     </row>
     <row r="474" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A474" s="3">
+      <c r="A474" s="9">
         <v>4519</v>
       </c>
       <c r="B474" s="4" t="s">
@@ -29448,7 +29456,7 @@
       </c>
     </row>
     <row r="475" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A475" s="3">
+      <c r="A475" s="9">
         <v>4521</v>
       </c>
       <c r="B475" s="4" t="s">
@@ -29489,7 +29497,7 @@
       </c>
     </row>
     <row r="476" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A476" s="3">
+      <c r="A476" s="9">
         <v>4522</v>
       </c>
       <c r="B476" s="4" t="s">
@@ -29530,7 +29538,7 @@
       </c>
     </row>
     <row r="477" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A477" s="3">
+      <c r="A477" s="9">
         <v>4523</v>
       </c>
       <c r="B477" s="4" t="s">
@@ -29571,7 +29579,7 @@
       </c>
     </row>
     <row r="478" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A478" s="3">
+      <c r="A478" s="9">
         <v>4524</v>
       </c>
       <c r="B478" s="4" t="s">
@@ -29612,7 +29620,7 @@
       </c>
     </row>
     <row r="479" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="3">
+      <c r="A479" s="9">
         <v>4525</v>
       </c>
       <c r="B479" s="4" t="s">
@@ -29653,7 +29661,7 @@
       </c>
     </row>
     <row r="480" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="3">
+      <c r="A480" s="9">
         <v>4530</v>
       </c>
       <c r="B480" s="4" t="s">
@@ -29694,7 +29702,7 @@
       </c>
     </row>
     <row r="481" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A481" s="3">
+      <c r="A481" s="9">
         <v>4532</v>
       </c>
       <c r="B481" s="4" t="s">
@@ -29735,7 +29743,7 @@
       </c>
     </row>
     <row r="482" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A482" s="3">
+      <c r="A482" s="9">
         <v>4535</v>
       </c>
       <c r="B482" s="4" t="s">
@@ -29776,7 +29784,7 @@
       </c>
     </row>
     <row r="483" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A483" s="3">
+      <c r="A483" s="9">
         <v>4540</v>
       </c>
       <c r="B483" s="4" t="s">
@@ -29817,7 +29825,7 @@
       </c>
     </row>
     <row r="484" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A484" s="3">
+      <c r="A484" s="9">
         <v>4542</v>
       </c>
       <c r="B484" s="4" t="s">
@@ -29858,7 +29866,7 @@
       </c>
     </row>
     <row r="485" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A485" s="3">
+      <c r="A485" s="9">
         <v>4543</v>
       </c>
       <c r="B485" s="4" t="s">
@@ -29899,7 +29907,7 @@
       </c>
     </row>
     <row r="486" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A486" s="3">
+      <c r="A486" s="9">
         <v>4550</v>
       </c>
       <c r="B486" s="4" t="s">
@@ -29940,7 +29948,7 @@
       </c>
     </row>
     <row r="487" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A487" s="3">
+      <c r="A487" s="9">
         <v>4560</v>
       </c>
       <c r="B487" s="4" t="s">
@@ -29981,7 +29989,7 @@
       </c>
     </row>
     <row r="488" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A488" s="3">
+      <c r="A488" s="9">
         <v>4801</v>
       </c>
       <c r="B488" s="4" t="s">
@@ -30022,7 +30030,7 @@
       </c>
     </row>
     <row r="489" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A489" s="3">
+      <c r="A489" s="9">
         <v>4805</v>
       </c>
       <c r="B489" s="4" t="s">
@@ -30063,7 +30071,7 @@
       </c>
     </row>
     <row r="490" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A490" s="3">
+      <c r="A490" s="9">
         <v>4806</v>
       </c>
       <c r="B490" s="4" t="s">
@@ -30104,7 +30112,7 @@
       </c>
     </row>
     <row r="491" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A491" s="3">
+      <c r="A491" s="9">
         <v>4808</v>
       </c>
       <c r="B491" s="4" t="s">
@@ -30145,7 +30153,7 @@
       </c>
     </row>
     <row r="492" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A492" s="3">
+      <c r="A492" s="9">
         <v>4810</v>
       </c>
       <c r="B492" s="4" t="s">
@@ -30186,7 +30194,7 @@
       </c>
     </row>
     <row r="493" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A493" s="6">
+      <c r="A493" s="22">
         <v>4811</v>
       </c>
       <c r="B493" s="7" t="s">
@@ -30227,7 +30235,7 @@
       </c>
     </row>
     <row r="494" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A494" s="3">
+      <c r="A494" s="9">
         <v>4812</v>
       </c>
       <c r="B494" s="4" t="s">
@@ -30268,7 +30276,7 @@
       </c>
     </row>
     <row r="495" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A495" s="3">
+      <c r="A495" s="9">
         <v>4814</v>
       </c>
       <c r="B495" s="4" t="s">
@@ -30309,7 +30317,7 @@
       </c>
     </row>
     <row r="496" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A496" s="6">
+      <c r="A496" s="22">
         <v>4816</v>
       </c>
       <c r="B496" s="7" t="s">
@@ -30350,7 +30358,7 @@
       </c>
     </row>
     <row r="497" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A497" s="3">
+      <c r="A497" s="9">
         <v>4818</v>
       </c>
       <c r="B497" s="4" t="s">
@@ -30391,7 +30399,7 @@
       </c>
     </row>
     <row r="498" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A498" s="3">
+      <c r="A498" s="9">
         <v>4820</v>
       </c>
       <c r="B498" s="4" t="s">
@@ -30432,7 +30440,7 @@
       </c>
     </row>
     <row r="499" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A499" s="3">
+      <c r="A499" s="9">
         <v>4822</v>
       </c>
       <c r="B499" s="4" t="s">
@@ -30473,7 +30481,7 @@
       </c>
     </row>
     <row r="500" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A500" s="3">
+      <c r="A500" s="9">
         <v>4824</v>
       </c>
       <c r="B500" s="4" t="s">
@@ -30514,7 +30522,7 @@
       </c>
     </row>
     <row r="501" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A501" s="3">
+      <c r="A501" s="9">
         <v>4826</v>
       </c>
       <c r="B501" s="4" t="s">
@@ -30555,7 +30563,7 @@
       </c>
     </row>
     <row r="502" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A502" s="3">
+      <c r="A502" s="9">
         <v>4828</v>
       </c>
       <c r="B502" s="4" t="s">
@@ -30596,7 +30604,7 @@
       </c>
     </row>
     <row r="503" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A503" s="3">
+      <c r="A503" s="9">
         <v>4830</v>
       </c>
       <c r="B503" s="4" t="s">
@@ -30637,7 +30645,7 @@
       </c>
     </row>
     <row r="504" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A504" s="3">
+      <c r="A504" s="9">
         <v>4832</v>
       </c>
       <c r="B504" s="4" t="s">
@@ -30678,7 +30686,7 @@
       </c>
     </row>
     <row r="505" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A505" s="3">
+      <c r="A505" s="9">
         <v>4834</v>
       </c>
       <c r="B505" s="4" t="s">
@@ -30719,7 +30727,7 @@
       </c>
     </row>
     <row r="506" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="6">
+      <c r="A506" s="22">
         <v>4836</v>
       </c>
       <c r="B506" s="7" t="s">
@@ -30760,7 +30768,7 @@
       </c>
     </row>
     <row r="507" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="6">
+      <c r="A507" s="22">
         <v>4838</v>
       </c>
       <c r="B507" s="7" t="s">
@@ -30801,7 +30809,7 @@
       </c>
     </row>
     <row r="508" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A508" s="6">
+      <c r="A508" s="22">
         <v>4840</v>
       </c>
       <c r="B508" s="7" t="s">
@@ -30842,7 +30850,7 @@
       </c>
     </row>
     <row r="509" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="3">
+      <c r="A509" s="9">
         <v>4842</v>
       </c>
       <c r="B509" s="4" t="s">
@@ -30883,7 +30891,7 @@
       </c>
     </row>
     <row r="510" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="6">
+      <c r="A510" s="22">
         <v>4844</v>
       </c>
       <c r="B510" s="7" t="s">
@@ -30924,7 +30932,7 @@
       </c>
     </row>
     <row r="511" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A511" s="3">
+      <c r="A511" s="9">
         <v>4845</v>
       </c>
       <c r="B511" s="4" t="s">
@@ -30965,7 +30973,7 @@
       </c>
     </row>
     <row r="512" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A512" s="3">
+      <c r="A512" s="9">
         <v>4860</v>
       </c>
       <c r="B512" s="4" t="s">
@@ -31006,7 +31014,7 @@
       </c>
     </row>
     <row r="513" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A513" s="6">
+      <c r="A513" s="22">
         <v>4862</v>
       </c>
       <c r="B513" s="7" t="s">
@@ -31047,7 +31055,7 @@
       </c>
     </row>
     <row r="514" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A514" s="3">
+      <c r="A514" s="9">
         <v>4864</v>
       </c>
       <c r="B514" s="4" t="s">
@@ -31088,7 +31096,7 @@
       </c>
     </row>
     <row r="515" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A515" s="6">
+      <c r="A515" s="22">
         <v>4866</v>
       </c>
       <c r="B515" s="7" t="s">
@@ -31129,7 +31137,7 @@
       </c>
     </row>
     <row r="516" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A516" s="6">
+      <c r="A516" s="22">
         <v>4868</v>
       </c>
       <c r="B516" s="7" t="s">
@@ -31170,7 +31178,7 @@
       </c>
     </row>
     <row r="517" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A517" s="3">
+      <c r="A517" s="9">
         <v>4870</v>
       </c>
       <c r="B517" s="4" t="s">
@@ -31211,7 +31219,7 @@
       </c>
     </row>
     <row r="518" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A518" s="6">
+      <c r="A518" s="22">
         <v>4872</v>
       </c>
       <c r="B518" s="7" t="s">
@@ -31252,7 +31260,7 @@
       </c>
     </row>
     <row r="519" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A519" s="6">
+      <c r="A519" s="22">
         <v>4874</v>
       </c>
       <c r="B519" s="7" t="s">
@@ -31293,7 +31301,7 @@
       </c>
     </row>
     <row r="520" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A520" s="3">
+      <c r="A520" s="9">
         <v>4875</v>
       </c>
       <c r="B520" s="4" t="s">
@@ -31334,7 +31342,7 @@
       </c>
     </row>
     <row r="521" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A521" s="3">
+      <c r="A521" s="9">
         <v>4876</v>
       </c>
       <c r="B521" s="4" t="s">
@@ -31375,7 +31383,7 @@
       </c>
     </row>
     <row r="522" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A522" s="3">
+      <c r="A522" s="9">
         <v>4878</v>
       </c>
       <c r="B522" s="4" t="s">
@@ -31416,7 +31424,7 @@
       </c>
     </row>
     <row r="523" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A523" s="3">
+      <c r="A523" s="9">
         <v>4880</v>
       </c>
       <c r="B523" s="4" t="s">
@@ -31457,7 +31465,7 @@
       </c>
     </row>
     <row r="524" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A524" s="3">
+      <c r="A524" s="9">
         <v>4882</v>
       </c>
       <c r="B524" s="4" t="s">
@@ -31498,7 +31506,7 @@
       </c>
     </row>
     <row r="525" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A525" s="6">
+      <c r="A525" s="22">
         <v>4884</v>
       </c>
       <c r="B525" s="7" t="s">
@@ -31539,7 +31547,7 @@
       </c>
     </row>
     <row r="526" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A526" s="3">
+      <c r="A526" s="9">
         <v>4890</v>
       </c>
       <c r="B526" s="4" t="s">
@@ -31580,7 +31588,7 @@
       </c>
     </row>
     <row r="527" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A527" s="3">
+      <c r="A527" s="9">
         <v>4891</v>
       </c>
       <c r="B527" s="4" t="s">
@@ -31621,7 +31629,7 @@
       </c>
     </row>
     <row r="528" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A528" s="3">
+      <c r="A528" s="9">
         <v>5101</v>
       </c>
       <c r="B528" s="4" t="s">
@@ -31662,7 +31670,7 @@
       </c>
     </row>
     <row r="529" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A529" s="3">
+      <c r="A529" s="9">
         <v>5105</v>
       </c>
       <c r="B529" s="4" t="s">
@@ -31703,7 +31711,7 @@
       </c>
     </row>
     <row r="530" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A530" s="3">
+      <c r="A530" s="9">
         <v>5108</v>
       </c>
       <c r="B530" s="4" t="s">
@@ -31744,7 +31752,7 @@
       </c>
     </row>
     <row r="531" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A531" s="3">
+      <c r="A531" s="9">
         <v>5110</v>
       </c>
       <c r="B531" s="4" t="s">
@@ -31785,7 +31793,7 @@
       </c>
     </row>
     <row r="532" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A532" s="3">
+      <c r="A532" s="9">
         <v>5111</v>
       </c>
       <c r="B532" s="4" t="s">
@@ -31826,7 +31834,7 @@
       </c>
     </row>
     <row r="533" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A533" s="3">
+      <c r="A533" s="9">
         <v>5112</v>
       </c>
       <c r="B533" s="4" t="s">
@@ -31867,7 +31875,7 @@
       </c>
     </row>
     <row r="534" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A534" s="3">
+      <c r="A534" s="9">
         <v>5113</v>
       </c>
       <c r="B534" s="4" t="s">
@@ -31908,7 +31916,7 @@
       </c>
     </row>
     <row r="535" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A535" s="3">
+      <c r="A535" s="9">
         <v>5114</v>
       </c>
       <c r="B535" s="4" t="s">
@@ -31949,7 +31957,7 @@
       </c>
     </row>
     <row r="536" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A536" s="3">
+      <c r="A536" s="9">
         <v>5115</v>
       </c>
       <c r="B536" s="4" t="s">
@@ -31990,7 +31998,7 @@
       </c>
     </row>
     <row r="537" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="3">
+      <c r="A537" s="9">
         <v>5116</v>
       </c>
       <c r="B537" s="4" t="s">
@@ -32031,7 +32039,7 @@
       </c>
     </row>
     <row r="538" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="3">
+      <c r="A538" s="9">
         <v>5117</v>
       </c>
       <c r="B538" s="4" t="s">
@@ -32072,7 +32080,7 @@
       </c>
     </row>
     <row r="539" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A539" s="3">
+      <c r="A539" s="9">
         <v>5118</v>
       </c>
       <c r="B539" s="4" t="s">
@@ -32113,7 +32121,7 @@
       </c>
     </row>
     <row r="540" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A540" s="3">
+      <c r="A540" s="9">
         <v>5119</v>
       </c>
       <c r="B540" s="4" t="s">
@@ -32154,7 +32162,7 @@
       </c>
     </row>
     <row r="541" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A541" s="3">
+      <c r="A541" s="9">
         <v>5120</v>
       </c>
       <c r="B541" s="4" t="s">
@@ -32195,7 +32203,7 @@
       </c>
     </row>
     <row r="542" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A542" s="3">
+      <c r="A542" s="9">
         <v>5121</v>
       </c>
       <c r="B542" s="4" t="s">
@@ -32236,7 +32244,7 @@
       </c>
     </row>
     <row r="543" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A543" s="3">
+      <c r="A543" s="9">
         <v>5122</v>
       </c>
       <c r="B543" s="4" t="s">
@@ -32277,7 +32285,7 @@
       </c>
     </row>
     <row r="544" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A544" s="3">
+      <c r="A544" s="9">
         <v>5123</v>
       </c>
       <c r="B544" s="4" t="s">
@@ -32318,7 +32326,7 @@
       </c>
     </row>
     <row r="545" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A545" s="3">
+      <c r="A545" s="9">
         <v>5125</v>
       </c>
       <c r="B545" s="4" t="s">
@@ -32359,7 +32367,7 @@
       </c>
     </row>
     <row r="546" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A546" s="3">
+      <c r="A546" s="9">
         <v>5126</v>
       </c>
       <c r="B546" s="4" t="s">
@@ -32400,7 +32408,7 @@
       </c>
     </row>
     <row r="547" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A547" s="3">
+      <c r="A547" s="9">
         <v>5127</v>
       </c>
       <c r="B547" s="4" t="s">
@@ -32441,7 +32449,7 @@
       </c>
     </row>
     <row r="548" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A548" s="3">
+      <c r="A548" s="9">
         <v>5130</v>
       </c>
       <c r="B548" s="4" t="s">
@@ -32482,7 +32490,7 @@
       </c>
     </row>
     <row r="549" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A549" s="3">
+      <c r="A549" s="9">
         <v>5134</v>
       </c>
       <c r="B549" s="4" t="s">
@@ -32523,7 +32531,7 @@
       </c>
     </row>
     <row r="550" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A550" s="3">
+      <c r="A550" s="9">
         <v>5136</v>
       </c>
       <c r="B550" s="4" t="s">
@@ -32564,7 +32572,7 @@
       </c>
     </row>
     <row r="551" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A551" s="3">
+      <c r="A551" s="9">
         <v>5145</v>
       </c>
       <c r="B551" s="4" t="s">
@@ -32605,7 +32613,7 @@
       </c>
     </row>
     <row r="552" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A552" s="3">
+      <c r="A552" s="9">
         <v>5150</v>
       </c>
       <c r="B552" s="4" t="s">
@@ -32646,7 +32654,7 @@
       </c>
     </row>
     <row r="553" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A553" s="3">
+      <c r="A553" s="9">
         <v>5152</v>
       </c>
       <c r="B553" s="4" t="s">
@@ -32687,7 +32695,7 @@
       </c>
     </row>
     <row r="554" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A554" s="3">
+      <c r="A554" s="9">
         <v>5160</v>
       </c>
       <c r="B554" s="4" t="s">
@@ -32728,7 +32736,7 @@
       </c>
     </row>
     <row r="555" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A555" s="3">
+      <c r="A555" s="9">
         <v>5164</v>
       </c>
       <c r="B555" s="4" t="s">
@@ -32769,7 +32777,7 @@
       </c>
     </row>
     <row r="556" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A556" s="3">
+      <c r="A556" s="9">
         <v>5170</v>
       </c>
       <c r="B556" s="4" t="s">
@@ -32810,7 +32818,7 @@
       </c>
     </row>
     <row r="557" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A557" s="3">
+      <c r="A557" s="9">
         <v>5172</v>
       </c>
       <c r="B557" s="4" t="s">
@@ -32851,7 +32859,7 @@
       </c>
     </row>
     <row r="558" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A558" s="3">
+      <c r="A558" s="9">
         <v>5180</v>
       </c>
       <c r="B558" s="4" t="s">
@@ -32892,7 +32900,7 @@
       </c>
     </row>
     <row r="559" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="3">
+      <c r="A559" s="9">
         <v>5401</v>
       </c>
       <c r="B559" s="4" t="s">
@@ -32933,7 +32941,7 @@
       </c>
     </row>
     <row r="560" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="3">
+      <c r="A560" s="9">
         <v>5410</v>
       </c>
       <c r="B560" s="4" t="s">
@@ -32974,7 +32982,7 @@
       </c>
     </row>
     <row r="561" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="3">
+      <c r="A561" s="9">
         <v>5412</v>
       </c>
       <c r="B561" s="4" t="s">
@@ -33015,7 +33023,7 @@
       </c>
     </row>
     <row r="562" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A562" s="3">
+      <c r="A562" s="9">
         <v>5413</v>
       </c>
       <c r="B562" s="4" t="s">
@@ -33056,7 +33064,7 @@
       </c>
     </row>
     <row r="563" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A563" s="3">
+      <c r="A563" s="9">
         <v>5414</v>
       </c>
       <c r="B563" s="4" t="s">
@@ -33097,7 +33105,7 @@
       </c>
     </row>
     <row r="564" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A564" s="3">
+      <c r="A564" s="9">
         <v>5415</v>
       </c>
       <c r="B564" s="4" t="s">
@@ -33138,7 +33146,7 @@
       </c>
     </row>
     <row r="565" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A565" s="3">
+      <c r="A565" s="9">
         <v>5420</v>
       </c>
       <c r="B565" s="4" t="s">
@@ -33179,7 +33187,7 @@
       </c>
     </row>
     <row r="566" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A566" s="3">
+      <c r="A566" s="9">
         <v>5425</v>
       </c>
       <c r="B566" s="4" t="s">
@@ -33220,7 +33228,7 @@
       </c>
     </row>
     <row r="567" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A567" s="3">
+      <c r="A567" s="9">
         <v>5430</v>
       </c>
       <c r="B567" s="4" t="s">
@@ -33261,7 +33269,7 @@
       </c>
     </row>
     <row r="568" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A568" s="3">
+      <c r="A568" s="9">
         <v>5440</v>
       </c>
       <c r="B568" s="4" t="s">
@@ -33302,7 +33310,7 @@
       </c>
     </row>
     <row r="569" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A569" s="3">
+      <c r="A569" s="9">
         <v>5445</v>
       </c>
       <c r="B569" s="4" t="s">
@@ -33343,7 +33351,7 @@
       </c>
     </row>
     <row r="570" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A570" s="3">
+      <c r="A570" s="9">
         <v>5450</v>
       </c>
       <c r="B570" s="4" t="s">
@@ -33384,7 +33392,7 @@
       </c>
     </row>
     <row r="571" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A571" s="3">
+      <c r="A571" s="9">
         <v>5455</v>
       </c>
       <c r="B571" s="4" t="s">
@@ -33425,7 +33433,7 @@
       </c>
     </row>
     <row r="572" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A572" s="3">
+      <c r="A572" s="9">
         <v>5462</v>
       </c>
       <c r="B572" s="4" t="s">
@@ -33466,7 +33474,7 @@
       </c>
     </row>
     <row r="573" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A573" s="3">
+      <c r="A573" s="9">
         <v>5703</v>
       </c>
       <c r="B573" s="4" t="s">
@@ -33507,7 +33515,7 @@
       </c>
     </row>
     <row r="574" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A574" s="3">
+      <c r="A574" s="9">
         <v>5704</v>
       </c>
       <c r="B574" s="4" t="s">
@@ -33548,7 +33556,7 @@
       </c>
     </row>
     <row r="575" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A575" s="3">
+      <c r="A575" s="9">
         <v>5712</v>
       </c>
       <c r="B575" s="4" t="s">
@@ -33589,7 +33597,7 @@
       </c>
     </row>
     <row r="576" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A576" s="3">
+      <c r="A576" s="9">
         <v>5715</v>
       </c>
       <c r="B576" s="4" t="s">
@@ -33630,7 +33638,7 @@
       </c>
     </row>
     <row r="577" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A577" s="6">
+      <c r="A577" s="22">
         <v>5725</v>
       </c>
       <c r="B577" s="7" t="s">
@@ -33671,7 +33679,7 @@
       </c>
     </row>
     <row r="578" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A578" s="6">
+      <c r="A578" s="22">
         <v>5732</v>
       </c>
       <c r="B578" s="7" t="s">
@@ -33712,7 +33720,7 @@
       </c>
     </row>
     <row r="579" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A579" s="3">
+      <c r="A579" s="9">
         <v>5740</v>
       </c>
       <c r="B579" s="4" t="s">
@@ -33753,7 +33761,7 @@
       </c>
     </row>
     <row r="580" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A580" s="3">
+      <c r="A580" s="9">
         <v>5746</v>
       </c>
       <c r="B580" s="4" t="s">
@@ -33794,7 +33802,7 @@
       </c>
     </row>
     <row r="581" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A581" s="3">
+      <c r="A581" s="9">
         <v>5750</v>
       </c>
       <c r="B581" s="4" t="s">
@@ -33835,7 +33843,7 @@
       </c>
     </row>
     <row r="582" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A582" s="3">
+      <c r="A582" s="9">
         <v>5755</v>
       </c>
       <c r="B582" s="4" t="s">
@@ -33876,7 +33884,7 @@
       </c>
     </row>
     <row r="583" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A583" s="3">
+      <c r="A583" s="9">
         <v>5765</v>
       </c>
       <c r="B583" s="4" t="s">
@@ -33917,7 +33925,7 @@
       </c>
     </row>
     <row r="584" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A584" s="3">
+      <c r="A584" s="9">
         <v>6001</v>
       </c>
       <c r="B584" s="4" t="s">
@@ -33958,7 +33966,7 @@
       </c>
     </row>
     <row r="585" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A585" s="3">
+      <c r="A585" s="9">
         <v>6005</v>
       </c>
       <c r="B585" s="4" t="s">
@@ -33999,7 +34007,7 @@
       </c>
     </row>
     <row r="586" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A586" s="3">
+      <c r="A586" s="9">
         <v>6010</v>
       </c>
       <c r="B586" s="4" t="s">
@@ -34040,7 +34048,7 @@
       </c>
     </row>
     <row r="587" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A587" s="3">
+      <c r="A587" s="9">
         <v>6011</v>
       </c>
       <c r="B587" s="4" t="s">
@@ -34081,7 +34089,7 @@
       </c>
     </row>
     <row r="588" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A588" s="3">
+      <c r="A588" s="9">
         <v>6012</v>
       </c>
       <c r="B588" s="4" t="s">
@@ -34122,7 +34130,7 @@
       </c>
     </row>
     <row r="589" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A589" s="3">
+      <c r="A589" s="9">
         <v>6013</v>
       </c>
       <c r="B589" s="4" t="s">
@@ -34163,7 +34171,7 @@
       </c>
     </row>
     <row r="590" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A590" s="3">
+      <c r="A590" s="9">
         <v>6014</v>
       </c>
       <c r="B590" s="4" t="s">
@@ -34204,7 +34212,7 @@
       </c>
     </row>
     <row r="591" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A591" s="3">
+      <c r="A591" s="9">
         <v>6015</v>
       </c>
       <c r="B591" s="4" t="s">
@@ -34245,7 +34253,7 @@
       </c>
     </row>
     <row r="592" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A592" s="3">
+      <c r="A592" s="9">
         <v>6016</v>
       </c>
       <c r="B592" s="4" t="s">
@@ -34286,7 +34294,7 @@
       </c>
     </row>
     <row r="593" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A593" s="3">
+      <c r="A593" s="9">
         <v>6017</v>
       </c>
       <c r="B593" s="4" t="s">
@@ -34327,7 +34335,7 @@
       </c>
     </row>
     <row r="594" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A594" s="3">
+      <c r="A594" s="9">
         <v>6020</v>
       </c>
       <c r="B594" s="4" t="s">
@@ -34368,7 +34376,7 @@
       </c>
     </row>
     <row r="595" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A595" s="3">
+      <c r="A595" s="9">
         <v>6022</v>
       </c>
       <c r="B595" s="4" t="s">
@@ -34409,7 +34417,7 @@
       </c>
     </row>
     <row r="596" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A596" s="3">
+      <c r="A596" s="9">
         <v>6024</v>
       </c>
       <c r="B596" s="4" t="s">
@@ -34450,7 +34458,7 @@
       </c>
     </row>
     <row r="597" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="3">
+      <c r="A597" s="9">
         <v>6025</v>
       </c>
       <c r="B597" s="4" t="s">
@@ -34491,7 +34499,7 @@
       </c>
     </row>
     <row r="598" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="3">
+      <c r="A598" s="9">
         <v>6026</v>
       </c>
       <c r="B598" s="4" t="s">
@@ -34532,7 +34540,7 @@
       </c>
     </row>
     <row r="599" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="3">
+      <c r="A599" s="9">
         <v>6027</v>
       </c>
       <c r="B599" s="4" t="s">
@@ -34573,7 +34581,7 @@
       </c>
     </row>
     <row r="600" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A600" s="3">
+      <c r="A600" s="9">
         <v>6029</v>
       </c>
       <c r="B600" s="4" t="s">
@@ -34614,7 +34622,7 @@
       </c>
     </row>
     <row r="601" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A601" s="3">
+      <c r="A601" s="9">
         <v>6030</v>
       </c>
       <c r="B601" s="4" t="s">
@@ -34655,7 +34663,7 @@
       </c>
     </row>
     <row r="602" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A602" s="3">
+      <c r="A602" s="9">
         <v>6032</v>
       </c>
       <c r="B602" s="9" t="s">
@@ -34696,7 +34704,7 @@
       </c>
     </row>
     <row r="603" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A603" s="3">
+      <c r="A603" s="9">
         <v>6033</v>
       </c>
       <c r="B603" s="4" t="s">
@@ -34737,7 +34745,7 @@
       </c>
     </row>
     <row r="604" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A604" s="3">
+      <c r="A604" s="9">
         <v>6035</v>
       </c>
       <c r="B604" s="4" t="s">
@@ -34778,7 +34786,7 @@
       </c>
     </row>
     <row r="605" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A605" s="3">
+      <c r="A605" s="9">
         <v>6037</v>
       </c>
       <c r="B605" s="4" t="s">
@@ -34819,7 +34827,7 @@
       </c>
     </row>
     <row r="606" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A606" s="3">
+      <c r="A606" s="9">
         <v>6038</v>
       </c>
       <c r="B606" s="4" t="s">
@@ -34860,7 +34868,7 @@
       </c>
     </row>
     <row r="607" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="3">
+      <c r="A607" s="9">
         <v>6039</v>
       </c>
       <c r="B607" s="4" t="s">
@@ -34901,7 +34909,7 @@
       </c>
     </row>
     <row r="608" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="3">
+      <c r="A608" s="9">
         <v>6040</v>
       </c>
       <c r="B608" s="4" t="s">
@@ -34942,7 +34950,7 @@
       </c>
     </row>
     <row r="609" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A609" s="3">
+      <c r="A609" s="9">
         <v>6041</v>
       </c>
       <c r="B609" s="4" t="s">
@@ -34983,7 +34991,7 @@
       </c>
     </row>
     <row r="610" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A610" s="3">
+      <c r="A610" s="9">
         <v>6042</v>
       </c>
       <c r="B610" s="4" t="s">
@@ -35024,7 +35032,7 @@
       </c>
     </row>
     <row r="611" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A611" s="3">
+      <c r="A611" s="9">
         <v>6043</v>
       </c>
       <c r="B611" s="4" t="s">
@@ -35065,7 +35073,7 @@
       </c>
     </row>
     <row r="612" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A612" s="3">
+      <c r="A612" s="9">
         <v>6044</v>
       </c>
       <c r="B612" s="4" t="s">
@@ -35106,7 +35114,7 @@
       </c>
     </row>
     <row r="613" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A613" s="3">
+      <c r="A613" s="9">
         <v>6045</v>
       </c>
       <c r="B613" s="4" t="s">
@@ -35147,7 +35155,7 @@
       </c>
     </row>
     <row r="614" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="3">
+      <c r="A614" s="9">
         <v>6046</v>
       </c>
       <c r="B614" s="4" t="s">
@@ -35188,7 +35196,7 @@
       </c>
     </row>
     <row r="615" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="6">
+      <c r="A615" s="22">
         <v>6048</v>
       </c>
       <c r="B615" s="7" t="s">
@@ -35229,7 +35237,7 @@
       </c>
     </row>
     <row r="616" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A616" s="3">
+      <c r="A616" s="9">
         <v>6050</v>
       </c>
       <c r="B616" s="4" t="s">
@@ -35270,7 +35278,7 @@
       </c>
     </row>
     <row r="617" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A617" s="3">
+      <c r="A617" s="9">
         <v>6052</v>
       </c>
       <c r="B617" s="4" t="s">
@@ -35311,7 +35319,7 @@
       </c>
     </row>
     <row r="618" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A618" s="3">
+      <c r="A618" s="9">
         <v>6053</v>
       </c>
       <c r="B618" s="4" t="s">
@@ -35352,7 +35360,7 @@
       </c>
     </row>
     <row r="619" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A619" s="3">
+      <c r="A619" s="9">
         <v>6054</v>
       </c>
       <c r="B619" s="4" t="s">
@@ -35393,7 +35401,7 @@
       </c>
     </row>
     <row r="620" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A620" s="3">
+      <c r="A620" s="9">
         <v>6055</v>
       </c>
       <c r="B620" s="4" t="s">
@@ -35434,7 +35442,7 @@
       </c>
     </row>
     <row r="621" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A621" s="3">
+      <c r="A621" s="9">
         <v>6056</v>
       </c>
       <c r="B621" s="4" t="s">
@@ -35475,7 +35483,7 @@
       </c>
     </row>
     <row r="622" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A622" s="3">
+      <c r="A622" s="9">
         <v>6057</v>
       </c>
       <c r="B622" s="4" t="s">
@@ -35516,7 +35524,7 @@
       </c>
     </row>
     <row r="623" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A623" s="3">
+      <c r="A623" s="9">
         <v>6058</v>
       </c>
       <c r="B623" s="4" t="s">
@@ -35557,7 +35565,7 @@
       </c>
     </row>
     <row r="624" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A624" s="3">
+      <c r="A624" s="9">
         <v>6060</v>
       </c>
       <c r="B624" s="4" t="s">
@@ -35598,7 +35606,7 @@
       </c>
     </row>
     <row r="625" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A625" s="3">
+      <c r="A625" s="9">
         <v>6062</v>
       </c>
       <c r="B625" s="4" t="s">
@@ -35639,7 +35647,7 @@
       </c>
     </row>
     <row r="626" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A626" s="3">
+      <c r="A626" s="9">
         <v>6063</v>
       </c>
       <c r="B626" s="4" t="s">
@@ -35680,7 +35688,7 @@
       </c>
     </row>
     <row r="627" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A627" s="3">
+      <c r="A627" s="9">
         <v>6064</v>
       </c>
       <c r="B627" s="4" t="s">
@@ -35721,7 +35729,7 @@
       </c>
     </row>
     <row r="628" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A628" s="3">
+      <c r="A628" s="9">
         <v>6065</v>
       </c>
       <c r="B628" s="4" t="s">
@@ -35762,7 +35770,7 @@
       </c>
     </row>
     <row r="629" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A629" s="3">
+      <c r="A629" s="9">
         <v>6066</v>
       </c>
       <c r="B629" s="4" t="s">
@@ -35803,7 +35811,7 @@
       </c>
     </row>
     <row r="630" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A630" s="3">
+      <c r="A630" s="9">
         <v>6067</v>
       </c>
       <c r="B630" s="4" t="s">
@@ -35844,7 +35852,7 @@
       </c>
     </row>
     <row r="631" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A631" s="6">
+      <c r="A631" s="22">
         <v>6068</v>
       </c>
       <c r="B631" s="7" t="s">
@@ -35885,7 +35893,7 @@
       </c>
     </row>
     <row r="632" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A632" s="3">
+      <c r="A632" s="9">
         <v>6072</v>
       </c>
       <c r="B632" s="4" t="s">
@@ -35926,7 +35934,7 @@
       </c>
     </row>
     <row r="633" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A633" s="3">
+      <c r="A633" s="9">
         <v>6074</v>
       </c>
       <c r="B633" s="4" t="s">
@@ -35967,7 +35975,7 @@
       </c>
     </row>
     <row r="634" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A634" s="3">
+      <c r="A634" s="9">
         <v>6076</v>
       </c>
       <c r="B634" s="4" t="s">
@@ -36008,7 +36016,7 @@
       </c>
     </row>
     <row r="635" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A635" s="3">
+      <c r="A635" s="9">
         <v>6077</v>
       </c>
       <c r="B635" s="4" t="s">
@@ -36049,7 +36057,7 @@
       </c>
     </row>
     <row r="636" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A636" s="3">
+      <c r="A636" s="9">
         <v>6078</v>
       </c>
       <c r="B636" s="4" t="s">
@@ -36090,7 +36098,7 @@
       </c>
     </row>
     <row r="637" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A637" s="3">
+      <c r="A637" s="9">
         <v>6079</v>
       </c>
       <c r="B637" s="4" t="s">
@@ -36131,7 +36139,7 @@
       </c>
     </row>
     <row r="638" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A638" s="3">
+      <c r="A638" s="9">
         <v>6080</v>
       </c>
       <c r="B638" s="4" t="s">
@@ -36172,7 +36180,7 @@
       </c>
     </row>
     <row r="639" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A639" s="3">
+      <c r="A639" s="9">
         <v>6081</v>
       </c>
       <c r="B639" s="4" t="s">
@@ -36213,7 +36221,7 @@
       </c>
     </row>
     <row r="640" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A640" s="3">
+      <c r="A640" s="9">
         <v>6303</v>
       </c>
       <c r="B640" s="4" t="s">
@@ -36254,7 +36262,7 @@
       </c>
     </row>
     <row r="641" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A641" s="3">
+      <c r="A641" s="9">
         <v>6305</v>
       </c>
       <c r="B641" s="4" t="s">
@@ -36295,7 +36303,7 @@
       </c>
     </row>
     <row r="642" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A642" s="3">
+      <c r="A642" s="9">
         <v>6310</v>
       </c>
       <c r="B642" s="4" t="s">
@@ -36336,7 +36344,7 @@
       </c>
     </row>
     <row r="643" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A643" s="3">
+      <c r="A643" s="9">
         <v>6314</v>
       </c>
       <c r="B643" s="4" t="s">
@@ -36377,7 +36385,7 @@
       </c>
     </row>
     <row r="644" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A644" s="3">
+      <c r="A644" s="9">
         <v>6315</v>
       </c>
       <c r="B644" s="4" t="s">
@@ -36418,7 +36426,7 @@
       </c>
     </row>
     <row r="645" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A645" s="3">
+      <c r="A645" s="9">
         <v>6320</v>
       </c>
       <c r="B645" s="4" t="s">
@@ -36459,7 +36467,7 @@
       </c>
     </row>
     <row r="646" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A646" s="3">
+      <c r="A646" s="9">
         <v>6324</v>
       </c>
       <c r="B646" s="4" t="s">
@@ -36500,7 +36508,7 @@
       </c>
     </row>
     <row r="647" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A647" s="3">
+      <c r="A647" s="9">
         <v>6330</v>
       </c>
       <c r="B647" s="4" t="s">
@@ -36541,7 +36549,7 @@
       </c>
     </row>
     <row r="648" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A648" s="3">
+      <c r="A648" s="9">
         <v>6335</v>
       </c>
       <c r="B648" s="4" t="s">
@@ -36582,7 +36590,7 @@
       </c>
     </row>
     <row r="649" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A649" s="3">
+      <c r="A649" s="9">
         <v>6340</v>
       </c>
       <c r="B649" s="4" t="s">
@@ -36623,7 +36631,7 @@
       </c>
     </row>
     <row r="650" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A650" s="3">
+      <c r="A650" s="9">
         <v>6350</v>
       </c>
       <c r="B650" s="4" t="s">
@@ -36664,7 +36672,7 @@
       </c>
     </row>
     <row r="651" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A651" s="3">
+      <c r="A651" s="9">
         <v>6360</v>
       </c>
       <c r="B651" s="4" t="s">
@@ -36705,7 +36713,7 @@
       </c>
     </row>
     <row r="652" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A652" s="3">
+      <c r="A652" s="9">
         <v>6362</v>
       </c>
       <c r="B652" s="4" t="s">
@@ -36746,7 +36754,7 @@
       </c>
     </row>
     <row r="653" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A653" s="3">
+      <c r="A653" s="9">
         <v>6364</v>
       </c>
       <c r="B653" s="4" t="s">
@@ -36787,7 +36795,7 @@
       </c>
     </row>
     <row r="654" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A654" s="3">
+      <c r="A654" s="9">
         <v>6366</v>
       </c>
       <c r="B654" s="4" t="s">
@@ -36828,7 +36836,7 @@
       </c>
     </row>
     <row r="655" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A655" s="3">
+      <c r="A655" s="9">
         <v>6368</v>
       </c>
       <c r="B655" s="4" t="s">
@@ -36869,7 +36877,7 @@
       </c>
     </row>
     <row r="656" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A656" s="6">
+      <c r="A656" s="22">
         <v>6370</v>
       </c>
       <c r="B656" s="7" t="s">
@@ -36910,7 +36918,7 @@
       </c>
     </row>
     <row r="657" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A657" s="6">
+      <c r="A657" s="22">
         <v>6372</v>
       </c>
       <c r="B657" s="7" t="s">
@@ -36951,7 +36959,7 @@
       </c>
     </row>
     <row r="658" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A658" s="3">
+      <c r="A658" s="9">
         <v>6380</v>
       </c>
       <c r="B658" s="4" t="s">
@@ -36992,7 +37000,7 @@
       </c>
     </row>
     <row r="659" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A659" s="3">
+      <c r="A659" s="9">
         <v>6382</v>
       </c>
       <c r="B659" s="4" t="s">
@@ -37033,7 +37041,7 @@
       </c>
     </row>
     <row r="660" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A660" s="3">
+      <c r="A660" s="9">
         <v>6601</v>
       </c>
       <c r="B660" s="4" t="s">
@@ -37074,7 +37082,7 @@
       </c>
     </row>
     <row r="661" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A661" s="3">
+      <c r="A661" s="9">
         <v>6605</v>
       </c>
       <c r="B661" s="4" t="s">
@@ -37115,7 +37123,7 @@
       </c>
     </row>
     <row r="662" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A662" s="3">
+      <c r="A662" s="9">
         <v>6606</v>
       </c>
       <c r="B662" s="4" t="s">
@@ -37156,7 +37164,7 @@
       </c>
     </row>
     <row r="663" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A663" s="3">
+      <c r="A663" s="9">
         <v>6607</v>
       </c>
       <c r="B663" s="4" t="s">
@@ -37197,7 +37205,7 @@
       </c>
     </row>
     <row r="664" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A664" s="3">
+      <c r="A664" s="9">
         <v>6608</v>
       </c>
       <c r="B664" s="4" t="s">
@@ -37238,7 +37246,7 @@
       </c>
     </row>
     <row r="665" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A665" s="3">
+      <c r="A665" s="9">
         <v>6609</v>
       </c>
       <c r="B665" s="4" t="s">
@@ -37279,7 +37287,7 @@
       </c>
     </row>
     <row r="666" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A666" s="3">
+      <c r="A666" s="9">
         <v>6610</v>
       </c>
       <c r="B666" s="4" t="s">
@@ -37320,7 +37328,7 @@
       </c>
     </row>
     <row r="667" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A667" s="3">
+      <c r="A667" s="9">
         <v>6613</v>
       </c>
       <c r="B667" s="4" t="s">
@@ -37361,7 +37369,7 @@
       </c>
     </row>
     <row r="668" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A668" s="3">
+      <c r="A668" s="9">
         <v>6614</v>
       </c>
       <c r="B668" s="4" t="s">
@@ -37402,7 +37410,7 @@
       </c>
     </row>
     <row r="669" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A669" s="3">
+      <c r="A669" s="9">
         <v>6617</v>
       </c>
       <c r="B669" s="4" t="s">
@@ -37443,7 +37451,7 @@
       </c>
     </row>
     <row r="670" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A670" s="3">
+      <c r="A670" s="9">
         <v>6618</v>
       </c>
       <c r="B670" s="4" t="s">
@@ -37484,7 +37492,7 @@
       </c>
     </row>
     <row r="671" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A671" s="6">
+      <c r="A671" s="22">
         <v>6619</v>
       </c>
       <c r="B671" s="7" t="s">
@@ -37525,7 +37533,7 @@
       </c>
     </row>
     <row r="672" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A672" s="3">
+      <c r="A672" s="9">
         <v>6621</v>
       </c>
       <c r="B672" s="4" t="s">
@@ -37566,7 +37574,7 @@
       </c>
     </row>
     <row r="673" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A673" s="3">
+      <c r="A673" s="9">
         <v>6622</v>
       </c>
       <c r="B673" s="4" t="s">
@@ -37607,7 +37615,7 @@
       </c>
     </row>
     <row r="674" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A674" s="3">
+      <c r="A674" s="9">
         <v>6623</v>
       </c>
       <c r="B674" s="4" t="s">
@@ -37648,7 +37656,7 @@
       </c>
     </row>
     <row r="675" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A675" s="3">
+      <c r="A675" s="9">
         <v>6624</v>
       </c>
       <c r="B675" s="4" t="s">
@@ -37689,7 +37697,7 @@
       </c>
     </row>
     <row r="676" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A676" s="3">
+      <c r="A676" s="9">
         <v>6625</v>
       </c>
       <c r="B676" s="4" t="s">
@@ -37730,7 +37738,7 @@
       </c>
     </row>
     <row r="677" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A677" s="3">
+      <c r="A677" s="9">
         <v>6626</v>
       </c>
       <c r="B677" s="4" t="s">
@@ -37771,7 +37779,7 @@
       </c>
     </row>
     <row r="678" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A678" s="3">
+      <c r="A678" s="9">
         <v>6627</v>
       </c>
       <c r="B678" s="4" t="s">
@@ -37812,7 +37820,7 @@
       </c>
     </row>
     <row r="679" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A679" s="3">
+      <c r="A679" s="9">
         <v>6628</v>
       </c>
       <c r="B679" s="4" t="s">
@@ -37853,7 +37861,7 @@
       </c>
     </row>
     <row r="680" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A680" s="6">
+      <c r="A680" s="22">
         <v>6630</v>
       </c>
       <c r="B680" s="7" t="s">
@@ -37894,7 +37902,7 @@
       </c>
     </row>
     <row r="681" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A681" s="3">
+      <c r="A681" s="9">
         <v>6631</v>
       </c>
       <c r="B681" s="4" t="s">
@@ -37935,7 +37943,7 @@
       </c>
     </row>
     <row r="682" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A682" s="6">
+      <c r="A682" s="22">
         <v>6632</v>
       </c>
       <c r="B682" s="7" t="s">
@@ -37976,7 +37984,7 @@
       </c>
     </row>
     <row r="683" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A683" s="6">
+      <c r="A683" s="22">
         <v>6633</v>
       </c>
       <c r="B683" s="7" t="s">
@@ -38017,7 +38025,7 @@
       </c>
     </row>
     <row r="684" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A684" s="3">
+      <c r="A684" s="9">
         <v>6634</v>
       </c>
       <c r="B684" s="4" t="s">
@@ -38058,7 +38066,7 @@
       </c>
     </row>
     <row r="685" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A685" s="3">
+      <c r="A685" s="9">
         <v>6635</v>
       </c>
       <c r="B685" s="4" t="s">
@@ -38099,7 +38107,7 @@
       </c>
     </row>
     <row r="686" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A686" s="3">
+      <c r="A686" s="9">
         <v>6638</v>
       </c>
       <c r="B686" s="4" t="s">
@@ -38140,7 +38148,7 @@
       </c>
     </row>
     <row r="687" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A687" s="3">
+      <c r="A687" s="9">
         <v>6639</v>
       </c>
       <c r="B687" s="4" t="s">
@@ -38181,7 +38189,7 @@
       </c>
     </row>
     <row r="688" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A688" s="3">
+      <c r="A688" s="9">
         <v>6640</v>
       </c>
       <c r="B688" s="4" t="s">
@@ -38222,7 +38230,7 @@
       </c>
     </row>
     <row r="689" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A689" s="3">
+      <c r="A689" s="9">
         <v>6641</v>
       </c>
       <c r="B689" s="4" t="s">
@@ -38263,7 +38271,7 @@
       </c>
     </row>
     <row r="690" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A690" s="3">
+      <c r="A690" s="9">
         <v>6642</v>
       </c>
       <c r="B690" s="4" t="s">
@@ -38304,7 +38312,7 @@
       </c>
     </row>
     <row r="691" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A691" s="3">
+      <c r="A691" s="9">
         <v>6645</v>
       </c>
       <c r="B691" s="4" t="s">
@@ -38345,7 +38353,7 @@
       </c>
     </row>
     <row r="692" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A692" s="3">
+      <c r="A692" s="9">
         <v>6646</v>
       </c>
       <c r="B692" s="4" t="s">
@@ -38386,7 +38394,7 @@
       </c>
     </row>
     <row r="693" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A693" s="3">
+      <c r="A693" s="9">
         <v>6647</v>
       </c>
       <c r="B693" s="4" t="s">
@@ -38427,7 +38435,7 @@
       </c>
     </row>
     <row r="694" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A694" s="3">
+      <c r="A694" s="9">
         <v>6648</v>
       </c>
       <c r="B694" s="4" t="s">
@@ -38468,7 +38476,7 @@
       </c>
     </row>
     <row r="695" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A695" s="3">
+      <c r="A695" s="9">
         <v>6649</v>
       </c>
       <c r="B695" s="4" t="s">
@@ -38509,7 +38517,7 @@
       </c>
     </row>
     <row r="696" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A696" s="3">
+      <c r="A696" s="9">
         <v>6650</v>
       </c>
       <c r="B696" s="4" t="s">
@@ -38550,7 +38558,7 @@
       </c>
     </row>
     <row r="697" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A697" s="3">
+      <c r="A697" s="9">
         <v>6651</v>
       </c>
       <c r="B697" s="4" t="s">
@@ -38591,7 +38599,7 @@
       </c>
     </row>
     <row r="698" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A698" s="3">
+      <c r="A698" s="9">
         <v>6652</v>
       </c>
       <c r="B698" s="4" t="s">
@@ -38632,7 +38640,7 @@
       </c>
     </row>
     <row r="699" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A699" s="3">
+      <c r="A699" s="9">
         <v>6653</v>
       </c>
       <c r="B699" s="4" t="s">
@@ -38673,7 +38681,7 @@
       </c>
     </row>
     <row r="700" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A700" s="3">
+      <c r="A700" s="9">
         <v>6654</v>
       </c>
       <c r="B700" s="4" t="s">
@@ -38714,7 +38722,7 @@
       </c>
     </row>
     <row r="701" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A701" s="3">
+      <c r="A701" s="9">
         <v>6657</v>
       </c>
       <c r="B701" s="4" t="s">
@@ -38755,7 +38763,7 @@
       </c>
     </row>
     <row r="702" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A702" s="6">
+      <c r="A702" s="22">
         <v>6660</v>
       </c>
       <c r="B702" s="7" t="s">
@@ -38796,7 +38804,7 @@
       </c>
     </row>
     <row r="703" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A703" s="3">
+      <c r="A703" s="9">
         <v>6670</v>
       </c>
       <c r="B703" s="4" t="s">
@@ -38837,7 +38845,7 @@
       </c>
     </row>
     <row r="704" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A704" s="3">
+      <c r="A704" s="9">
         <v>6680</v>
       </c>
       <c r="B704" s="4" t="s">
@@ -38878,7 +38886,7 @@
       </c>
     </row>
     <row r="705" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A705" s="3">
+      <c r="A705" s="9">
         <v>6901</v>
       </c>
       <c r="B705" s="4" t="s">
@@ -38919,7 +38927,7 @@
       </c>
     </row>
     <row r="706" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A706" s="3">
+      <c r="A706" s="9">
         <v>6903</v>
       </c>
       <c r="B706" s="4" t="s">
@@ -38960,7 +38968,7 @@
       </c>
     </row>
     <row r="707" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A707" s="3">
+      <c r="A707" s="9">
         <v>6910</v>
       </c>
       <c r="B707" s="4" t="s">
@@ -39001,7 +39009,7 @@
       </c>
     </row>
     <row r="708" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A708" s="3">
+      <c r="A708" s="9">
         <v>6913</v>
       </c>
       <c r="B708" s="4" t="s">
@@ -39042,7 +39050,7 @@
       </c>
     </row>
     <row r="709" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A709" s="3">
+      <c r="A709" s="9">
         <v>6915</v>
       </c>
       <c r="B709" s="4" t="s">
@@ -39083,7 +39091,7 @@
       </c>
     </row>
     <row r="710" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A710" s="3">
+      <c r="A710" s="9">
         <v>6916</v>
       </c>
       <c r="B710" s="4" t="s">
@@ -39124,7 +39132,7 @@
       </c>
     </row>
     <row r="711" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A711" s="3">
+      <c r="A711" s="9">
         <v>6917</v>
       </c>
       <c r="B711" s="4" t="s">
@@ -39165,7 +39173,7 @@
       </c>
     </row>
     <row r="712" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A712" s="3">
+      <c r="A712" s="9">
         <v>6918</v>
       </c>
       <c r="B712" s="4" t="s">
@@ -39206,7 +39214,7 @@
       </c>
     </row>
     <row r="713" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A713" s="3">
+      <c r="A713" s="9">
         <v>6920</v>
       </c>
       <c r="B713" s="4" t="s">
@@ -39247,7 +39255,7 @@
       </c>
     </row>
     <row r="714" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A714" s="3">
+      <c r="A714" s="9">
         <v>6921</v>
       </c>
       <c r="B714" s="4" t="s">
@@ -39288,7 +39296,7 @@
       </c>
     </row>
     <row r="715" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A715" s="3">
+      <c r="A715" s="9">
         <v>6922</v>
       </c>
       <c r="B715" s="4" t="s">
@@ -39329,7 +39337,7 @@
       </c>
     </row>
     <row r="716" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A716" s="3">
+      <c r="A716" s="9">
         <v>6924</v>
       </c>
       <c r="B716" s="4" t="s">
@@ -39370,7 +39378,7 @@
       </c>
     </row>
     <row r="717" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="3">
+      <c r="A717" s="9">
         <v>6925</v>
       </c>
       <c r="B717" s="4" t="s">
@@ -39411,7 +39419,7 @@
       </c>
     </row>
     <row r="718" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="3">
+      <c r="A718" s="9">
         <v>6926</v>
       </c>
       <c r="B718" s="4" t="s">
@@ -39452,7 +39460,7 @@
       </c>
     </row>
     <row r="719" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A719" s="3">
+      <c r="A719" s="9">
         <v>6928</v>
       </c>
       <c r="B719" s="4" t="s">
@@ -39493,7 +39501,7 @@
       </c>
     </row>
     <row r="720" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A720" s="3">
+      <c r="A720" s="9">
         <v>6931</v>
       </c>
       <c r="B720" s="4" t="s">
@@ -39534,7 +39542,7 @@
       </c>
     </row>
     <row r="721" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A721" s="3">
+      <c r="A721" s="9">
         <v>6932</v>
       </c>
       <c r="B721" s="4" t="s">
@@ -39575,7 +39583,7 @@
       </c>
     </row>
     <row r="722" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A722" s="3">
+      <c r="A722" s="9">
         <v>6935</v>
       </c>
       <c r="B722" s="4" t="s">
@@ -39616,7 +39624,7 @@
       </c>
     </row>
     <row r="723" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A723" s="3">
+      <c r="A723" s="9">
         <v>6940</v>
       </c>
       <c r="B723" s="4" t="s">
@@ -39657,7 +39665,7 @@
       </c>
     </row>
     <row r="724" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A724" s="3">
+      <c r="A724" s="9">
         <v>6941</v>
       </c>
       <c r="B724" s="4" t="s">
@@ -39698,7 +39706,7 @@
       </c>
     </row>
     <row r="725" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A725" s="3">
+      <c r="A725" s="9">
         <v>6943</v>
       </c>
       <c r="B725" s="4" t="s">
@@ -39739,7 +39747,7 @@
       </c>
     </row>
     <row r="726" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A726" s="3">
+      <c r="A726" s="9">
         <v>6950</v>
       </c>
       <c r="B726" s="4" t="s">
@@ -39780,7 +39788,7 @@
       </c>
     </row>
     <row r="727" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A727" s="3">
+      <c r="A727" s="9">
         <v>6952</v>
       </c>
       <c r="B727" s="4" t="s">
@@ -39821,7 +39829,7 @@
       </c>
     </row>
     <row r="728" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A728" s="3">
+      <c r="A728" s="9">
         <v>6954</v>
       </c>
       <c r="B728" s="4" t="s">
@@ -39862,7 +39870,7 @@
       </c>
     </row>
     <row r="729" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A729" s="3">
+      <c r="A729" s="9">
         <v>6955</v>
       </c>
       <c r="B729" s="4" t="s">
@@ -39903,7 +39911,7 @@
       </c>
     </row>
     <row r="730" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="3">
+      <c r="A730" s="9">
         <v>6963</v>
       </c>
       <c r="B730" s="4" t="s">
@@ -39944,7 +39952,7 @@
       </c>
     </row>
     <row r="731" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A731" s="3">
+      <c r="A731" s="9">
         <v>6964</v>
       </c>
       <c r="B731" s="4" t="s">
@@ -39985,7 +39993,7 @@
       </c>
     </row>
     <row r="732" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A732" s="3">
+      <c r="A732" s="9">
         <v>6965</v>
       </c>
       <c r="B732" s="3" t="s">
@@ -40026,7 +40034,7 @@
       </c>
     </row>
     <row r="733" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A733" s="3">
+      <c r="A733" s="9">
         <v>6967</v>
       </c>
       <c r="B733" s="4" t="s">
@@ -40067,7 +40075,7 @@
       </c>
     </row>
     <row r="734" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A734" s="3">
+      <c r="A734" s="9">
         <v>6970</v>
       </c>
       <c r="B734" s="4" t="s">
@@ -40108,7 +40116,7 @@
       </c>
     </row>
     <row r="735" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A735" s="3">
+      <c r="A735" s="9">
         <v>6971</v>
       </c>
       <c r="B735" s="4" t="s">
@@ -40149,7 +40157,7 @@
       </c>
     </row>
     <row r="736" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A736" s="3">
+      <c r="A736" s="9">
         <v>6972</v>
       </c>
       <c r="B736" s="4" t="s">
@@ -40190,7 +40198,7 @@
       </c>
     </row>
     <row r="737" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A737" s="3">
+      <c r="A737" s="9">
         <v>6974</v>
       </c>
       <c r="B737" s="4" t="s">
@@ -40231,7 +40239,7 @@
       </c>
     </row>
     <row r="738" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="3">
+      <c r="A738" s="9">
         <v>6975</v>
       </c>
       <c r="B738" s="4" t="s">
@@ -40272,7 +40280,7 @@
       </c>
     </row>
     <row r="739" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="3">
+      <c r="A739" s="9">
         <v>6976</v>
       </c>
       <c r="B739" s="4" t="s">
@@ -40313,7 +40321,7 @@
       </c>
     </row>
     <row r="740" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A740" s="3">
+      <c r="A740" s="9">
         <v>6977</v>
       </c>
       <c r="B740" s="4" t="s">
@@ -40354,7 +40362,7 @@
       </c>
     </row>
     <row r="741" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A741" s="3">
+      <c r="A741" s="9">
         <v>6978</v>
       </c>
       <c r="B741" s="4" t="s">
@@ -40395,7 +40403,7 @@
       </c>
     </row>
     <row r="742" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A742" s="3">
+      <c r="A742" s="9">
         <v>6982</v>
       </c>
       <c r="B742" s="4" t="s">
@@ -40436,7 +40444,7 @@
       </c>
     </row>
     <row r="743" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A743" s="3">
+      <c r="A743" s="9">
         <v>7103</v>
       </c>
       <c r="B743" s="4" t="s">
@@ -40477,7 +40485,7 @@
       </c>
     </row>
     <row r="744" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A744" s="3">
+      <c r="A744" s="9">
         <v>7303</v>
       </c>
       <c r="B744" s="4" t="s">
@@ -40518,7 +40526,7 @@
       </c>
     </row>
     <row r="745" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A745" s="3">
+      <c r="A745" s="9">
         <v>7305</v>
       </c>
       <c r="B745" s="4" t="s">
@@ -40559,7 +40567,7 @@
       </c>
     </row>
     <row r="746" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A746" s="3">
+      <c r="A746" s="9">
         <v>7310</v>
       </c>
       <c r="B746" s="4" t="s">
@@ -40600,7 +40608,7 @@
       </c>
     </row>
     <row r="747" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A747" s="3">
+      <c r="A747" s="9">
         <v>7315</v>
       </c>
       <c r="B747" s="4" t="s">
@@ -40641,7 +40649,7 @@
       </c>
     </row>
     <row r="748" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A748" s="3">
+      <c r="A748" s="9">
         <v>7350</v>
       </c>
       <c r="B748" s="4" t="s">
@@ -40682,7 +40690,7 @@
       </c>
     </row>
     <row r="749" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="3">
+      <c r="A749" s="9">
         <v>7360</v>
       </c>
       <c r="B749" s="4" t="s">
@@ -40723,7 +40731,7 @@
       </c>
     </row>
     <row r="750" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="3">
+      <c r="A750" s="9">
         <v>7370</v>
       </c>
       <c r="B750" s="4" t="s">
@@ -40764,7 +40772,7 @@
       </c>
     </row>
     <row r="751" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A751" s="3">
+      <c r="A751" s="9">
         <v>7501</v>
       </c>
       <c r="B751" s="4" t="s">
@@ -40805,7 +40813,7 @@
       </c>
     </row>
     <row r="752" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A752" s="3">
+      <c r="A752" s="9">
         <v>7503</v>
       </c>
       <c r="B752" s="4" t="s">
@@ -40846,7 +40854,7 @@
       </c>
     </row>
     <row r="753" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A753" s="3">
+      <c r="A753" s="9">
         <v>7510</v>
       </c>
       <c r="B753" s="4" t="s">
@@ -40887,7 +40895,7 @@
       </c>
     </row>
     <row r="754" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A754" s="3">
+      <c r="A754" s="9">
         <v>7514</v>
       </c>
       <c r="B754" s="4" t="s">
@@ -40928,7 +40936,7 @@
       </c>
     </row>
     <row r="755" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A755" s="6">
+      <c r="A755" s="22">
         <v>7520</v>
       </c>
       <c r="B755" s="7" t="s">
@@ -40969,7 +40977,7 @@
       </c>
     </row>
     <row r="756" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A756" s="3">
+      <c r="A756" s="9">
         <v>7525</v>
       </c>
       <c r="B756" s="4" t="s">
@@ -41010,7 +41018,7 @@
       </c>
     </row>
     <row r="757" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A757" s="3">
+      <c r="A757" s="9">
         <v>7540</v>
       </c>
       <c r="B757" s="4" t="s">
@@ -41051,7 +41059,7 @@
       </c>
     </row>
     <row r="758" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A758" s="3">
+      <c r="A758" s="9">
         <v>7545</v>
       </c>
       <c r="B758" s="4" t="s">
@@ -41092,7 +41100,7 @@
       </c>
     </row>
     <row r="759" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A759" s="6">
+      <c r="A759" s="22">
         <v>7560</v>
       </c>
       <c r="B759" s="7" t="s">
@@ -41133,7 +41141,7 @@
       </c>
     </row>
     <row r="760" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A760" s="3">
+      <c r="A760" s="9">
         <v>7565</v>
       </c>
       <c r="B760" s="4" t="s">
@@ -41174,7 +41182,7 @@
       </c>
     </row>
     <row r="761" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A761" s="3">
+      <c r="A761" s="9">
         <v>7567</v>
       </c>
       <c r="B761" s="4" t="s">
@@ -41215,7 +41223,7 @@
       </c>
     </row>
     <row r="762" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A762" s="3">
+      <c r="A762" s="9">
         <v>7580</v>
       </c>
       <c r="B762" s="4" t="s">
@@ -41256,7 +41264,7 @@
       </c>
     </row>
     <row r="763" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A763" s="3">
+      <c r="A763" s="9">
         <v>7703</v>
       </c>
       <c r="B763" s="4" t="s">
@@ -41297,7 +41305,7 @@
       </c>
     </row>
     <row r="764" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A764" s="3">
+      <c r="A764" s="9">
         <v>7901</v>
       </c>
       <c r="B764" s="4" t="s">
@@ -41338,7 +41346,7 @@
       </c>
     </row>
     <row r="765" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A765" s="3">
+      <c r="A765" s="9">
         <v>7903</v>
       </c>
       <c r="B765" s="4" t="s">
@@ -41379,7 +41387,7 @@
       </c>
     </row>
     <row r="766" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A766" s="3">
+      <c r="A766" s="9">
         <v>7910</v>
       </c>
       <c r="B766" s="4" t="s">
@@ -41420,7 +41428,7 @@
       </c>
     </row>
     <row r="767" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A767" s="3">
+      <c r="A767" s="9">
         <v>7920</v>
       </c>
       <c r="B767" s="4" t="s">
@@ -41461,7 +41469,7 @@
       </c>
     </row>
     <row r="768" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A768" s="3">
+      <c r="A768" s="9">
         <v>7930</v>
       </c>
       <c r="B768" s="4" t="s">
@@ -41502,7 +41510,7 @@
       </c>
     </row>
     <row r="769" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A769" s="3">
+      <c r="A769" s="9">
         <v>7935</v>
       </c>
       <c r="B769" s="4" t="s">
@@ -41543,7 +41551,7 @@
       </c>
     </row>
     <row r="770" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A770" s="3">
+      <c r="A770" s="9">
         <v>7940</v>
       </c>
       <c r="B770" s="4" t="s">
@@ -41584,7 +41592,7 @@
       </c>
     </row>
     <row r="771" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A771" s="3">
+      <c r="A771" s="9">
         <v>7950</v>
       </c>
       <c r="B771" s="4" t="s">
@@ -41625,7 +41633,7 @@
       </c>
     </row>
     <row r="772" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A772" s="3">
+      <c r="A772" s="9">
         <v>7960</v>
       </c>
       <c r="B772" s="4" t="s">
@@ -41666,7 +41674,7 @@
       </c>
     </row>
     <row r="773" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A773" s="3">
+      <c r="A773" s="9">
         <v>8103</v>
       </c>
       <c r="B773" s="4" t="s">
@@ -41707,7 +41715,7 @@
       </c>
     </row>
     <row r="774" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A774" s="3">
+      <c r="A774" s="9">
         <v>8110</v>
       </c>
       <c r="B774" s="4" t="s">
@@ -41748,7 +41756,7 @@
       </c>
     </row>
     <row r="775" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="3">
+      <c r="A775" s="9">
         <v>8303</v>
       </c>
       <c r="B775" s="4" t="s">
@@ -41789,7 +41797,7 @@
       </c>
     </row>
     <row r="776" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="3">
+      <c r="A776" s="9">
         <v>8315</v>
       </c>
       <c r="B776" s="4" t="s">
@@ -41830,7 +41838,7 @@
       </c>
     </row>
     <row r="777" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A777" s="3">
+      <c r="A777" s="9">
         <v>8420</v>
       </c>
       <c r="B777" s="4" t="s">
@@ -41871,7 +41879,7 @@
       </c>
     </row>
     <row r="778" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A778" s="3">
+      <c r="A778" s="9">
         <v>8503</v>
       </c>
       <c r="B778" s="4" t="s">
@@ -41912,7 +41920,7 @@
       </c>
     </row>
     <row r="779" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A779" s="3">
+      <c r="A779" s="9">
         <v>8505</v>
       </c>
       <c r="B779" s="4" t="s">
@@ -41953,7 +41961,7 @@
       </c>
     </row>
     <row r="780" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A780" s="3">
+      <c r="A780" s="9">
         <v>8510</v>
       </c>
       <c r="B780" s="4" t="s">
@@ -41994,7 +42002,7 @@
       </c>
     </row>
     <row r="781" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A781" s="3">
+      <c r="A781" s="9">
         <v>8520</v>
       </c>
       <c r="B781" s="4" t="s">
@@ -42035,7 +42043,7 @@
       </c>
     </row>
     <row r="782" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A782" s="3">
+      <c r="A782" s="9">
         <v>8601</v>
       </c>
       <c r="B782" s="4" t="s">
@@ -42076,7 +42084,7 @@
       </c>
     </row>
     <row r="783" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A783" s="3">
+      <c r="A783" s="9">
         <v>8603</v>
       </c>
       <c r="B783" s="4" t="s">
@@ -42117,7 +42125,7 @@
       </c>
     </row>
     <row r="784" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A784" s="3">
+      <c r="A784" s="9">
         <v>8610</v>
       </c>
       <c r="B784" s="4" t="s">
@@ -42158,7 +42166,7 @@
       </c>
     </row>
     <row r="785" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A785" s="3">
+      <c r="A785" s="9">
         <v>8615</v>
       </c>
       <c r="B785" s="4" t="s">
@@ -42199,7 +42207,7 @@
       </c>
     </row>
     <row r="786" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A786" s="3">
+      <c r="A786" s="9">
         <v>8620</v>
       </c>
       <c r="B786" s="4" t="s">
@@ -42240,7 +42248,7 @@
       </c>
     </row>
     <row r="787" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A787" s="3">
+      <c r="A787" s="9">
         <v>8623</v>
       </c>
       <c r="B787" s="4" t="s">
@@ -42281,7 +42289,7 @@
       </c>
     </row>
     <row r="788" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A788" s="6">
+      <c r="A788" s="22">
         <v>8630</v>
       </c>
       <c r="B788" s="7" t="s">
@@ -42322,7 +42330,7 @@
       </c>
     </row>
     <row r="789" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A789" s="3">
+      <c r="A789" s="9">
         <v>8635</v>
       </c>
       <c r="B789" s="4" t="s">
@@ -42363,7 +42371,7 @@
       </c>
     </row>
     <row r="790" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A790" s="3">
+      <c r="A790" s="9">
         <v>8640</v>
       </c>
       <c r="B790" s="4" t="s">
@@ -42404,7 +42412,7 @@
       </c>
     </row>
     <row r="791" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A791" s="3">
+      <c r="A791" s="9">
         <v>8645</v>
       </c>
       <c r="B791" s="4" t="s">
@@ -42445,7 +42453,7 @@
       </c>
     </row>
     <row r="792" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A792" s="3">
+      <c r="A792" s="9">
         <v>8646</v>
       </c>
       <c r="B792" s="4" t="s">
@@ -42486,7 +42494,7 @@
       </c>
     </row>
     <row r="793" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A793" s="3">
+      <c r="A793" s="9">
         <v>8648</v>
       </c>
       <c r="B793" s="4" t="s">
@@ -42527,7 +42535,7 @@
       </c>
     </row>
     <row r="794" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A794" s="6">
+      <c r="A794" s="22">
         <v>8650</v>
       </c>
       <c r="B794" s="7" t="s">
@@ -42568,7 +42576,7 @@
       </c>
     </row>
     <row r="795" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A795" s="3">
+      <c r="A795" s="9">
         <v>8660</v>
       </c>
       <c r="B795" s="4" t="s">
@@ -42609,7 +42617,7 @@
       </c>
     </row>
     <row r="796" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A796" s="3">
+      <c r="A796" s="9">
         <v>8663</v>
       </c>
       <c r="B796" s="4" t="s">
@@ -42650,7 +42658,7 @@
       </c>
     </row>
     <row r="797" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A797" s="3">
+      <c r="A797" s="9">
         <v>8665</v>
       </c>
       <c r="B797" s="4" t="s">
@@ -42692,7 +42700,7 @@
     </row>
     <row r="798" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="799" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A799" s="4">
+      <c r="A799" s="9">
         <v>1300</v>
       </c>
       <c r="B799" s="4" t="s">
@@ -42711,7 +42719,7 @@
       </c>
     </row>
     <row r="800" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A800" s="4">
+      <c r="A800" s="9">
         <v>1500</v>
       </c>
       <c r="B800" s="4" t="s">
@@ -42730,7 +42738,7 @@
       </c>
     </row>
     <row r="801" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A801" s="4">
+      <c r="A801" s="9">
         <v>1600</v>
       </c>
       <c r="B801" s="4" t="s">
@@ -42749,7 +42757,7 @@
       </c>
     </row>
     <row r="802" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A802" s="4">
+      <c r="A802" s="9">
         <v>1800</v>
       </c>
       <c r="B802" s="4" t="s">
@@ -42768,7 +42776,7 @@
       </c>
     </row>
     <row r="803" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A803" s="4">
+      <c r="A803" s="9">
         <v>3000</v>
       </c>
       <c r="B803" s="4" t="s">
@@ -42787,7 +42795,7 @@
       </c>
     </row>
     <row r="804" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A804" s="4">
+      <c r="A804" s="9">
         <v>3900</v>
       </c>
       <c r="B804" s="4" t="s">
@@ -42806,7 +42814,7 @@
       </c>
     </row>
     <row r="805" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A805" s="4">
+      <c r="A805" s="9">
         <v>6000</v>
       </c>
       <c r="B805" s="4" t="s">
@@ -42825,7 +42833,7 @@
       </c>
     </row>
     <row r="806" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A806" s="4">
+      <c r="A806" s="9">
         <v>6900</v>
       </c>
       <c r="B806" s="4" t="s">
@@ -42845,7 +42853,7 @@
     </row>
     <row r="807" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="808" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A808" s="4">
+      <c r="A808" s="9">
         <v>9000</v>
       </c>
       <c r="B808" s="4" t="s">
@@ -42874,7 +42882,7 @@
       </c>
     </row>
     <row r="809" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A809" s="4">
+      <c r="A809" s="9">
         <v>9000</v>
       </c>
       <c r="B809" s="4" t="s">
@@ -42903,7 +42911,7 @@
       </c>
     </row>
     <row r="810" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A810" s="4">
+      <c r="A810" s="9">
         <v>9000</v>
       </c>
       <c r="B810" s="4" t="s">
@@ -42932,7 +42940,7 @@
       </c>
     </row>
     <row r="811" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A811" s="4">
+      <c r="A811" s="9">
         <v>9000</v>
       </c>
       <c r="B811" s="4" t="s">
@@ -42961,7 +42969,7 @@
       </c>
     </row>
     <row r="812" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A812" s="19"/>
+      <c r="A812" s="24"/>
       <c r="B812" s="19"/>
       <c r="C812" s="19"/>
       <c r="D812" s="19"/>
